--- a/research/traditional_assets/database/data/canada/canada_software_internet.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_software_internet.xlsx
@@ -2013,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2150,22 +2150,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1005705269765737</v>
+        <v>0.1003370900800858</v>
       </c>
       <c r="C2">
-        <v>35.30307917408089</v>
+        <v>35.02827708316443</v>
       </c>
       <c r="D2">
-        <v>31.61307917408089</v>
+        <v>31.69707708316443</v>
       </c>
       <c r="E2">
-        <v>-2.88</v>
+        <v>-2.5212</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3588</v>
       </c>
       <c r="G2">
         <v>3.69</v>
@@ -2186,28 +2186,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01804764</v>
       </c>
       <c r="N2">
-        <v>2.928469387755102</v>
+        <v>2.910421747755102</v>
       </c>
       <c r="O2">
-        <v>0.7760443877551021</v>
+        <v>0.7712617631551021</v>
       </c>
       <c r="P2">
-        <v>2.152425</v>
+        <v>2.1391599846</v>
       </c>
       <c r="Q2">
-        <v>2.897425</v>
+        <v>2.8841599846</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1005705269765737</v>
+        <v>0.1009771566465513</v>
       </c>
       <c r="T2">
-        <v>1.264908244262672</v>
+        <v>1.274299229712501</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>162.2632869314272</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2232,22 +2232,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1003370900800858</v>
+        <v>0.1001036531835979</v>
       </c>
       <c r="C3">
-        <v>35.02827708316443</v>
+        <v>34.75392255674698</v>
       </c>
       <c r="D3">
-        <v>31.69707708316443</v>
+        <v>31.78152255674697</v>
       </c>
       <c r="E3">
-        <v>-2.5212</v>
+        <v>-2.1624</v>
       </c>
       <c r="F3">
-        <v>0.3588</v>
+        <v>0.7176</v>
       </c>
       <c r="G3">
         <v>3.69</v>
@@ -2268,28 +2268,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M3">
-        <v>0.01804764</v>
+        <v>0.03609528</v>
       </c>
       <c r="N3">
-        <v>2.910421747755102</v>
+        <v>2.892374107755102</v>
       </c>
       <c r="O3">
-        <v>0.7712617631551021</v>
+        <v>0.7664791385551021</v>
       </c>
       <c r="P3">
-        <v>2.1391599846</v>
+        <v>2.1258949692</v>
       </c>
       <c r="Q3">
-        <v>2.8841599846</v>
+        <v>2.8708949692</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1009771566465513</v>
+        <v>0.1013920848812223</v>
       </c>
       <c r="T3">
-        <v>1.274299229712501</v>
+        <v>1.283881867926612</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>162.2632869314272</v>
+        <v>81.13164346571358</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2314,22 +2314,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1001036531835979</v>
+        <v>0.09987021628710996</v>
       </c>
       <c r="C4">
-        <v>34.75392255674698</v>
+        <v>34.48001918150836</v>
       </c>
       <c r="D4">
-        <v>31.78152255674697</v>
+        <v>31.86641918150836</v>
       </c>
       <c r="E4">
-        <v>-2.1624</v>
+        <v>-1.8036</v>
       </c>
       <c r="F4">
-        <v>0.7176</v>
+        <v>1.0764</v>
       </c>
       <c r="G4">
         <v>3.69</v>
@@ -2350,28 +2350,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M4">
-        <v>0.03609528</v>
+        <v>0.05414292</v>
       </c>
       <c r="N4">
-        <v>2.892374107755102</v>
+        <v>2.874326467755102</v>
       </c>
       <c r="O4">
-        <v>0.7664791385551021</v>
+        <v>0.7616965139551021</v>
       </c>
       <c r="P4">
-        <v>2.1258949692</v>
+        <v>2.1126299538</v>
       </c>
       <c r="Q4">
-        <v>2.8708949692</v>
+        <v>2.8576299538</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1013920848812223</v>
+        <v>0.1018155683372268</v>
       </c>
       <c r="T4">
-        <v>1.283881867926612</v>
+        <v>1.293662086310087</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>81.13164346571358</v>
+        <v>54.08776231047572</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2396,22 +2396,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09987021628710996</v>
+        <v>0.09963677939062203</v>
       </c>
       <c r="C5">
-        <v>34.48001918150836</v>
+        <v>34.20657058255486</v>
       </c>
       <c r="D5">
-        <v>31.86641918150836</v>
+        <v>31.95177058255486</v>
       </c>
       <c r="E5">
-        <v>-1.8036</v>
+        <v>-1.4448</v>
       </c>
       <c r="F5">
-        <v>1.0764</v>
+        <v>1.4352</v>
       </c>
       <c r="G5">
         <v>3.69</v>
@@ -2432,28 +2432,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M5">
-        <v>0.05414292</v>
+        <v>0.07219056</v>
       </c>
       <c r="N5">
-        <v>2.874326467755102</v>
+        <v>2.856278827755102</v>
       </c>
       <c r="O5">
-        <v>0.7616965139551021</v>
+        <v>0.7569138893551021</v>
       </c>
       <c r="P5">
-        <v>2.1126299538</v>
+        <v>2.0993649384</v>
       </c>
       <c r="Q5">
-        <v>2.8576299538</v>
+        <v>2.8443649384</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1018155683372268</v>
+        <v>0.1022478743652313</v>
       </c>
       <c r="T5">
-        <v>1.293662086310087</v>
+        <v>1.303646059243217</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>54.08776231047572</v>
+        <v>40.56582173285679</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2478,22 +2478,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09963677939062203</v>
+        <v>0.09940334249413411</v>
       </c>
       <c r="C6">
-        <v>34.20657058255486</v>
+        <v>33.93358042393515</v>
       </c>
       <c r="D6">
-        <v>31.95177058255486</v>
+        <v>32.03758042393515</v>
       </c>
       <c r="E6">
-        <v>-1.4448</v>
+        <v>-1.086</v>
       </c>
       <c r="F6">
-        <v>1.4352</v>
+        <v>1.794</v>
       </c>
       <c r="G6">
         <v>3.69</v>
@@ -2514,28 +2514,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M6">
-        <v>0.07219056</v>
+        <v>0.0902382</v>
       </c>
       <c r="N6">
-        <v>2.856278827755102</v>
+        <v>2.838231187755102</v>
       </c>
       <c r="O6">
-        <v>0.7569138893551021</v>
+        <v>0.7521312647551021</v>
       </c>
       <c r="P6">
-        <v>2.0993649384</v>
+        <v>2.086099923</v>
       </c>
       <c r="Q6">
-        <v>2.8443649384</v>
+        <v>2.831099923</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1022478743652313</v>
+        <v>0.1026892815727728</v>
       </c>
       <c r="T6">
-        <v>1.303646059243217</v>
+        <v>1.313840221080202</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>40.56582173285679</v>
+        <v>32.45265738628543</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2560,22 +2560,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09940334249413411</v>
+        <v>0.0991699055976462</v>
       </c>
       <c r="C7">
-        <v>33.93358042393515</v>
+        <v>33.66105240916463</v>
       </c>
       <c r="D7">
-        <v>32.03758042393515</v>
+        <v>32.12385240916463</v>
       </c>
       <c r="E7">
-        <v>-1.086</v>
+        <v>-0.7271999999999994</v>
       </c>
       <c r="F7">
-        <v>1.794</v>
+        <v>2.1528</v>
       </c>
       <c r="G7">
         <v>3.69</v>
@@ -2596,28 +2596,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M7">
-        <v>0.0902382</v>
+        <v>0.10828584</v>
       </c>
       <c r="N7">
-        <v>2.838231187755102</v>
+        <v>2.820183547755102</v>
       </c>
       <c r="O7">
-        <v>0.7521312647551021</v>
+        <v>0.7473486401551021</v>
       </c>
       <c r="P7">
-        <v>2.086099923</v>
+        <v>2.0728349076</v>
       </c>
       <c r="Q7">
-        <v>2.831099923</v>
+        <v>2.8178349076</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1026892815727728</v>
+        <v>0.1031400804230279</v>
       </c>
       <c r="T7">
-        <v>1.313840221080202</v>
+        <v>1.324251279977549</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>32.45265738628543</v>
+        <v>27.04388115523785</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2642,22 +2642,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09916990559764619</v>
+        <v>0.09893646870115827</v>
       </c>
       <c r="C8">
-        <v>33.66105240916463</v>
+        <v>33.3889902817583</v>
       </c>
       <c r="D8">
-        <v>32.12385240916463</v>
+        <v>32.2105902817583</v>
       </c>
       <c r="E8">
-        <v>-0.7271999999999998</v>
+        <v>-0.3683999999999998</v>
       </c>
       <c r="F8">
-        <v>2.1528</v>
+        <v>2.5116</v>
       </c>
       <c r="G8">
         <v>3.69</v>
@@ -2678,28 +2678,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M8">
-        <v>0.10828584</v>
+        <v>0.12633348</v>
       </c>
       <c r="N8">
-        <v>2.820183547755102</v>
+        <v>2.802135907755102</v>
       </c>
       <c r="O8">
-        <v>0.7473486401551021</v>
+        <v>0.742566015555102</v>
       </c>
       <c r="P8">
-        <v>2.0728349076</v>
+        <v>2.0595698922</v>
       </c>
       <c r="Q8">
-        <v>2.8178349076</v>
+        <v>2.8045698922</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1031400804230279</v>
+        <v>0.1036005738722132</v>
       </c>
       <c r="T8">
-        <v>1.324251279977549</v>
+        <v>1.334886232614624</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.04388115523786</v>
+        <v>23.18046956163245</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2724,22 +2724,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09893646870115826</v>
+        <v>0.09870303180467035</v>
       </c>
       <c r="C9">
-        <v>33.3889902817583</v>
+        <v>33.11739782577219</v>
       </c>
       <c r="D9">
-        <v>32.2105902817583</v>
+        <v>32.29779782577219</v>
       </c>
       <c r="E9">
-        <v>-0.3683999999999994</v>
+        <v>-0.009599999999999831</v>
       </c>
       <c r="F9">
-        <v>2.5116</v>
+        <v>2.8704</v>
       </c>
       <c r="G9">
         <v>3.69</v>
@@ -2760,28 +2760,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M9">
-        <v>0.12633348</v>
+        <v>0.14438112</v>
       </c>
       <c r="N9">
-        <v>2.802135907755102</v>
+        <v>2.784088267755102</v>
       </c>
       <c r="O9">
-        <v>0.742566015555102</v>
+        <v>0.7377833909551021</v>
       </c>
       <c r="P9">
-        <v>2.0595698922</v>
+        <v>2.0463048768</v>
       </c>
       <c r="Q9">
-        <v>2.8045698922</v>
+        <v>2.7913048768</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1036005738722132</v>
+        <v>0.1040710780485547</v>
       </c>
       <c r="T9">
-        <v>1.334886232614624</v>
+        <v>1.345752379874243</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.18046956163245</v>
+        <v>20.2829108664284</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2806,22 +2806,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09870303180467035</v>
+        <v>0.09846959490818243</v>
       </c>
       <c r="C10">
-        <v>33.11739782577219</v>
+        <v>32.84627886635368</v>
       </c>
       <c r="D10">
-        <v>32.29779782577219</v>
+        <v>32.38547886635368</v>
       </c>
       <c r="E10">
-        <v>-0.009599999999999831</v>
+        <v>0.3492000000000002</v>
       </c>
       <c r="F10">
-        <v>2.8704</v>
+        <v>3.2292</v>
       </c>
       <c r="G10">
         <v>3.69</v>
@@ -2842,28 +2842,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M10">
-        <v>0.14438112</v>
+        <v>0.16242876</v>
       </c>
       <c r="N10">
-        <v>2.784088267755102</v>
+        <v>2.766040627755102</v>
       </c>
       <c r="O10">
-        <v>0.7377833909551021</v>
+        <v>0.733000766355102</v>
       </c>
       <c r="P10">
-        <v>2.0463048768</v>
+        <v>2.0330398614</v>
       </c>
       <c r="Q10">
-        <v>2.7913048768</v>
+        <v>2.7780398614</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1040710780485547</v>
+        <v>0.1045519229760246</v>
       </c>
       <c r="T10">
-        <v>1.345752379874243</v>
+        <v>1.356857343557151</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.2829108664284</v>
+        <v>18.0292541034919</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2888,22 +2888,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09846959490818243</v>
+        <v>0.0982361580116945</v>
       </c>
       <c r="C11">
-        <v>32.84627886635368</v>
+        <v>32.57563727030076</v>
       </c>
       <c r="D11">
-        <v>32.38547886635368</v>
+        <v>32.47363727030076</v>
       </c>
       <c r="E11">
-        <v>0.3492000000000002</v>
+        <v>0.7080000000000002</v>
       </c>
       <c r="F11">
-        <v>3.2292</v>
+        <v>3.588</v>
       </c>
       <c r="G11">
         <v>3.69</v>
@@ -2924,28 +2924,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M11">
-        <v>0.16242876</v>
+        <v>0.1804764</v>
       </c>
       <c r="N11">
-        <v>2.766040627755102</v>
+        <v>2.747992987755102</v>
       </c>
       <c r="O11">
-        <v>0.733000766355102</v>
+        <v>0.7282181417551021</v>
       </c>
       <c r="P11">
-        <v>2.0330398614</v>
+        <v>2.019774846</v>
       </c>
       <c r="Q11">
-        <v>2.7780398614</v>
+        <v>2.764774846</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1045519229760246</v>
+        <v>0.1050434533463272</v>
       </c>
       <c r="T11">
-        <v>1.356857343557151</v>
+        <v>1.368209084210791</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.0292541034919</v>
+        <v>16.22632869314272</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2970,22 +2970,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0982361580116945</v>
+        <v>0.0980027211152066</v>
       </c>
       <c r="C12">
-        <v>32.57563727030076</v>
+        <v>32.30547694663052</v>
       </c>
       <c r="D12">
-        <v>32.47363727030076</v>
+        <v>32.56227694663053</v>
       </c>
       <c r="E12">
-        <v>0.7080000000000006</v>
+        <v>1.0668</v>
       </c>
       <c r="F12">
-        <v>3.588000000000001</v>
+        <v>3.9468</v>
       </c>
       <c r="G12">
         <v>3.69</v>
@@ -3006,28 +3006,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M12">
-        <v>0.1804764</v>
+        <v>0.19852404</v>
       </c>
       <c r="N12">
-        <v>2.747992987755102</v>
+        <v>2.729945347755102</v>
       </c>
       <c r="O12">
-        <v>0.7282181417551021</v>
+        <v>0.723435517155102</v>
       </c>
       <c r="P12">
-        <v>2.019774846</v>
+        <v>2.0065098306</v>
       </c>
       <c r="Q12">
-        <v>2.764774846</v>
+        <v>2.7515098306</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1050434533463272</v>
+        <v>0.1055460293429288</v>
       </c>
       <c r="T12">
-        <v>1.368209084210791</v>
+        <v>1.379815920160018</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.22632869314272</v>
+        <v>14.75120790285701</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -3052,22 +3052,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0980027211152066</v>
+        <v>0.09776928421871867</v>
       </c>
       <c r="C13">
-        <v>32.30547694663052</v>
+        <v>32.03580184715689</v>
       </c>
       <c r="D13">
-        <v>32.56227694663053</v>
+        <v>32.65140184715689</v>
       </c>
       <c r="E13">
-        <v>1.0668</v>
+        <v>1.4256</v>
       </c>
       <c r="F13">
-        <v>3.9468</v>
+        <v>4.3056</v>
       </c>
       <c r="G13">
         <v>3.69</v>
@@ -3088,28 +3088,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M13">
-        <v>0.19852404</v>
+        <v>0.21657168</v>
       </c>
       <c r="N13">
-        <v>2.729945347755102</v>
+        <v>2.711897707755102</v>
       </c>
       <c r="O13">
-        <v>0.723435517155102</v>
+        <v>0.7186528925551021</v>
       </c>
       <c r="P13">
-        <v>2.0065098306</v>
+        <v>1.9932448152</v>
       </c>
       <c r="Q13">
-        <v>2.7515098306</v>
+        <v>2.7382448152</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1055460293429288</v>
+        <v>0.1060600275212712</v>
       </c>
       <c r="T13">
-        <v>1.379815920160018</v>
+        <v>1.391686547835363</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.75120790285701</v>
+        <v>13.52194057761893</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -3134,22 +3134,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09776928421871867</v>
+        <v>0.09767917232223075</v>
       </c>
       <c r="C14">
-        <v>32.03580184715689</v>
+        <v>31.71153671967639</v>
       </c>
       <c r="D14">
-        <v>32.65140184715689</v>
+        <v>32.68593671967639</v>
       </c>
       <c r="E14">
-        <v>1.4256</v>
+        <v>1.784400000000001</v>
       </c>
       <c r="F14">
-        <v>4.3056</v>
+        <v>4.664400000000001</v>
       </c>
       <c r="G14">
         <v>3.69</v>
@@ -3170,45 +3170,45 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M14">
-        <v>0.21657168</v>
+        <v>0.24161592</v>
       </c>
       <c r="N14">
-        <v>2.711897707755102</v>
+        <v>2.686853467755102</v>
       </c>
       <c r="O14">
-        <v>0.7186528925551021</v>
+        <v>0.712016168955102</v>
       </c>
       <c r="P14">
-        <v>1.9932448152</v>
+        <v>1.9748372988</v>
       </c>
       <c r="Q14">
-        <v>2.7382448152</v>
+        <v>2.7198372988</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1060600275212712</v>
+        <v>0.1065858417496905</v>
       </c>
       <c r="T14">
-        <v>1.391686547835363</v>
+        <v>1.403830063503245</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.265</v>
       </c>
       <c r="W14">
-        <v>0.0369705</v>
+        <v>0.038073</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.52194057761893</v>
+        <v>12.12034946933588</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -3216,22 +3216,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09767917232223075</v>
+        <v>0.09745676042574283</v>
       </c>
       <c r="C15">
-        <v>31.71153671967639</v>
+        <v>31.43828830740175</v>
       </c>
       <c r="D15">
-        <v>32.68593671967639</v>
+        <v>32.77148830740175</v>
       </c>
       <c r="E15">
-        <v>1.784400000000001</v>
+        <v>2.143200000000001</v>
       </c>
       <c r="F15">
-        <v>4.664400000000001</v>
+        <v>5.023200000000001</v>
       </c>
       <c r="G15">
         <v>3.69</v>
@@ -3252,28 +3252,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M15">
-        <v>0.24161592</v>
+        <v>0.2602017600000001</v>
       </c>
       <c r="N15">
-        <v>2.686853467755102</v>
+        <v>2.668267627755102</v>
       </c>
       <c r="O15">
-        <v>0.712016168955102</v>
+        <v>0.707090921355102</v>
       </c>
       <c r="P15">
-        <v>1.9748372988</v>
+        <v>1.9611767064</v>
       </c>
       <c r="Q15">
-        <v>2.7198372988</v>
+        <v>2.7061767064</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1065858417496905</v>
+        <v>0.10712388421598</v>
       </c>
       <c r="T15">
-        <v>1.403830063503245</v>
+        <v>1.416255986512241</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.12034946933588</v>
+        <v>11.25461022152618</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3298,22 +3298,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09745676042574283</v>
+        <v>0.09723434852925492</v>
       </c>
       <c r="C16">
-        <v>31.43828830740175</v>
+        <v>31.16548891277722</v>
       </c>
       <c r="D16">
-        <v>32.77148830740175</v>
+        <v>32.85748891277722</v>
       </c>
       <c r="E16">
-        <v>2.143200000000001</v>
+        <v>2.502000000000002</v>
       </c>
       <c r="F16">
-        <v>5.023200000000001</v>
+        <v>5.382000000000001</v>
       </c>
       <c r="G16">
         <v>3.69</v>
@@ -3334,28 +3334,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M16">
-        <v>0.2602017600000001</v>
+        <v>0.2787876000000001</v>
       </c>
       <c r="N16">
-        <v>2.668267627755102</v>
+        <v>2.649681787755102</v>
       </c>
       <c r="O16">
-        <v>0.707090921355102</v>
+        <v>0.702165673755102</v>
       </c>
       <c r="P16">
-        <v>1.9611767064</v>
+        <v>1.947516114</v>
       </c>
       <c r="Q16">
-        <v>2.7061767064</v>
+        <v>2.692516114</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.10712388421598</v>
+        <v>0.1076745865050058</v>
       </c>
       <c r="T16">
-        <v>1.416255986512241</v>
+        <v>1.428974284180272</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.25461022152618</v>
+        <v>10.50430287342443</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3380,22 +3380,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09723434852925492</v>
+        <v>0.09701193663276698</v>
       </c>
       <c r="C17">
-        <v>31.16548891277722</v>
+        <v>30.89314208010877</v>
       </c>
       <c r="D17">
-        <v>32.85748891277722</v>
+        <v>32.94394208010878</v>
       </c>
       <c r="E17">
-        <v>2.502000000000001</v>
+        <v>2.8608</v>
       </c>
       <c r="F17">
-        <v>5.382000000000001</v>
+        <v>5.7408</v>
       </c>
       <c r="G17">
         <v>3.69</v>
@@ -3416,28 +3416,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M17">
-        <v>0.2787876</v>
+        <v>0.29737344</v>
       </c>
       <c r="N17">
-        <v>2.649681787755102</v>
+        <v>2.631095947755102</v>
       </c>
       <c r="O17">
-        <v>0.7021656737551021</v>
+        <v>0.6972404261551021</v>
       </c>
       <c r="P17">
-        <v>1.947516114</v>
+        <v>1.9338555216</v>
       </c>
       <c r="Q17">
-        <v>2.692516114</v>
+        <v>2.6788555216</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1076745865050058</v>
+        <v>0.108238400753294</v>
       </c>
       <c r="T17">
-        <v>1.428974284180272</v>
+        <v>1.441995398459447</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.50430287342443</v>
+        <v>9.847783943835408</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3462,22 +3462,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09701193663276698</v>
+        <v>0.09700193973627909</v>
       </c>
       <c r="C18">
-        <v>30.89314208010877</v>
+        <v>30.53823863367694</v>
       </c>
       <c r="D18">
-        <v>32.94394208010878</v>
+        <v>32.94783863367694</v>
       </c>
       <c r="E18">
-        <v>2.8608</v>
+        <v>3.219600000000001</v>
       </c>
       <c r="F18">
-        <v>5.7408</v>
+        <v>6.099600000000001</v>
       </c>
       <c r="G18">
         <v>3.69</v>
@@ -3498,45 +3498,45 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M18">
-        <v>0.29737344</v>
+        <v>0.3263286</v>
       </c>
       <c r="N18">
-        <v>2.631095947755102</v>
+        <v>2.602140787755102</v>
       </c>
       <c r="O18">
-        <v>0.6972404261551021</v>
+        <v>0.6895673087551021</v>
       </c>
       <c r="P18">
-        <v>1.9338555216</v>
+        <v>1.912573479</v>
       </c>
       <c r="Q18">
-        <v>2.6788555216</v>
+        <v>2.657573479</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.108238400753294</v>
+        <v>0.1088158008870832</v>
       </c>
       <c r="T18">
-        <v>1.441995398459447</v>
+        <v>1.455330274528481</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.265</v>
       </c>
       <c r="W18">
-        <v>0.038073</v>
+        <v>0.0393225</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>9.847783943835408</v>
+        <v>8.973989370699048</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3544,22 +3544,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09700193973627909</v>
+        <v>0.09679202283979116</v>
       </c>
       <c r="C19">
-        <v>30.53823863367694</v>
+        <v>30.26147269004575</v>
       </c>
       <c r="D19">
-        <v>32.94783863367694</v>
+        <v>33.02987269004576</v>
       </c>
       <c r="E19">
-        <v>3.219600000000001</v>
+        <v>3.578400000000001</v>
       </c>
       <c r="F19">
-        <v>6.099600000000001</v>
+        <v>6.458400000000001</v>
       </c>
       <c r="G19">
         <v>3.69</v>
@@ -3580,28 +3580,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M19">
-        <v>0.3263286</v>
+        <v>0.3455244000000001</v>
       </c>
       <c r="N19">
-        <v>2.602140787755102</v>
+        <v>2.582944987755102</v>
       </c>
       <c r="O19">
-        <v>0.6895673087551021</v>
+        <v>0.684480421755102</v>
       </c>
       <c r="P19">
-        <v>1.912573479</v>
+        <v>1.898464566</v>
       </c>
       <c r="Q19">
-        <v>2.657573479</v>
+        <v>2.643464566</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1088158008870832</v>
+        <v>0.1094072839509648</v>
       </c>
       <c r="T19">
-        <v>1.455330274528481</v>
+        <v>1.468990391477248</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.973989370699048</v>
+        <v>8.475434405660213</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3626,22 +3626,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09679202283979117</v>
+        <v>0.09658210594330323</v>
       </c>
       <c r="C20">
-        <v>30.26147269004575</v>
+        <v>29.98511626545669</v>
       </c>
       <c r="D20">
-        <v>33.02987269004576</v>
+        <v>33.11231626545669</v>
       </c>
       <c r="E20">
-        <v>3.5784</v>
+        <v>3.937200000000001</v>
       </c>
       <c r="F20">
-        <v>6.4584</v>
+        <v>6.817200000000001</v>
       </c>
       <c r="G20">
         <v>3.69</v>
@@ -3662,28 +3662,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M20">
-        <v>0.3455244</v>
+        <v>0.3647202</v>
       </c>
       <c r="N20">
-        <v>2.582944987755102</v>
+        <v>2.563749187755102</v>
       </c>
       <c r="O20">
-        <v>0.684480421755102</v>
+        <v>0.679393534755102</v>
       </c>
       <c r="P20">
-        <v>1.898464566</v>
+        <v>1.884355653</v>
       </c>
       <c r="Q20">
-        <v>2.643464566</v>
+        <v>2.629355653</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1094072839509648</v>
+        <v>0.1100133715349423</v>
       </c>
       <c r="T20">
-        <v>1.468990391477248</v>
+        <v>1.482987795264255</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.475434405660213</v>
+        <v>8.029358910625465</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3708,22 +3708,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09658210594330323</v>
+        <v>0.09637218904681533</v>
       </c>
       <c r="C21">
-        <v>29.98511626545669</v>
+        <v>29.70917243409925</v>
       </c>
       <c r="D21">
-        <v>33.11231626545669</v>
+        <v>33.19517243409926</v>
       </c>
       <c r="E21">
-        <v>3.937200000000001</v>
+        <v>4.296000000000001</v>
       </c>
       <c r="F21">
-        <v>6.817200000000001</v>
+        <v>7.176000000000001</v>
       </c>
       <c r="G21">
         <v>3.69</v>
@@ -3744,28 +3744,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M21">
-        <v>0.3647202</v>
+        <v>0.383916</v>
       </c>
       <c r="N21">
-        <v>2.563749187755102</v>
+        <v>2.544553387755102</v>
       </c>
       <c r="O21">
-        <v>0.679393534755102</v>
+        <v>0.6743066477551021</v>
       </c>
       <c r="P21">
-        <v>1.884355653</v>
+        <v>1.87024674</v>
       </c>
       <c r="Q21">
-        <v>2.629355653</v>
+        <v>2.61524674</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1100133715349423</v>
+        <v>0.1106346113085191</v>
       </c>
       <c r="T21">
-        <v>1.482987795264255</v>
+        <v>1.497335134145939</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.029358910625465</v>
+        <v>7.627890965094192</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3790,22 +3790,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09637218904681533</v>
+        <v>0.09628575215032741</v>
       </c>
       <c r="C22">
-        <v>29.70917243409925</v>
+        <v>29.38461053687478</v>
       </c>
       <c r="D22">
-        <v>33.19517243409926</v>
+        <v>33.22941053687479</v>
       </c>
       <c r="E22">
-        <v>4.296000000000001</v>
+        <v>4.654800000000002</v>
       </c>
       <c r="F22">
-        <v>7.176000000000001</v>
+        <v>7.534800000000001</v>
       </c>
       <c r="G22">
         <v>3.69</v>
@@ -3826,45 +3826,45 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M22">
-        <v>0.383916</v>
+        <v>0.4091396400000001</v>
       </c>
       <c r="N22">
-        <v>2.544553387755102</v>
+        <v>2.519329747755102</v>
       </c>
       <c r="O22">
-        <v>0.6743066477551021</v>
+        <v>0.667622383155102</v>
       </c>
       <c r="P22">
-        <v>1.87024674</v>
+        <v>1.8517073646</v>
       </c>
       <c r="Q22">
-        <v>2.61524674</v>
+        <v>2.5967073646</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1106346113085191</v>
+        <v>0.1112715786713005</v>
       </c>
       <c r="T22">
-        <v>1.497335134145939</v>
+        <v>1.512045696796778</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.265</v>
       </c>
       <c r="W22">
-        <v>0.0393225</v>
+        <v>0.0399105</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.627890965094192</v>
+        <v>7.157628108963241</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3872,22 +3872,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09628575215032741</v>
+        <v>0.09608171525383946</v>
       </c>
       <c r="C23">
-        <v>29.38461053687478</v>
+        <v>29.10691142436843</v>
       </c>
       <c r="D23">
-        <v>33.22941053687479</v>
+        <v>33.31051142436844</v>
       </c>
       <c r="E23">
-        <v>4.654800000000001</v>
+        <v>5.0136</v>
       </c>
       <c r="F23">
-        <v>7.534800000000001</v>
+        <v>7.8936</v>
       </c>
       <c r="G23">
         <v>3.69</v>
@@ -3908,28 +3908,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M23">
-        <v>0.40913964</v>
+        <v>0.42862248</v>
       </c>
       <c r="N23">
-        <v>2.519329747755102</v>
+        <v>2.499846907755102</v>
       </c>
       <c r="O23">
-        <v>0.6676223831551021</v>
+        <v>0.662459430555102</v>
       </c>
       <c r="P23">
-        <v>1.8517073646</v>
+        <v>1.8373874772</v>
       </c>
       <c r="Q23">
-        <v>2.5967073646</v>
+        <v>2.5823874772</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1112715786713005</v>
+        <v>0.1119248785305634</v>
       </c>
       <c r="T23">
-        <v>1.512045696796778</v>
+        <v>1.527133453361742</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.157628108963243</v>
+        <v>6.83228137673764</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3954,22 +3954,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09608171525383946</v>
+        <v>0.09587767835735156</v>
       </c>
       <c r="C24">
-        <v>29.10691142436843</v>
+        <v>28.82960915586537</v>
       </c>
       <c r="D24">
-        <v>33.31051142436844</v>
+        <v>33.39200915586537</v>
       </c>
       <c r="E24">
-        <v>5.0136</v>
+        <v>5.372400000000002</v>
       </c>
       <c r="F24">
-        <v>7.8936</v>
+        <v>8.252400000000002</v>
       </c>
       <c r="G24">
         <v>3.69</v>
@@ -3990,28 +3990,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M24">
-        <v>0.42862248</v>
+        <v>0.4481053200000001</v>
       </c>
       <c r="N24">
-        <v>2.499846907755102</v>
+        <v>2.480364067755102</v>
       </c>
       <c r="O24">
-        <v>0.662459430555102</v>
+        <v>0.657296477955102</v>
       </c>
       <c r="P24">
-        <v>1.8373874772</v>
+        <v>1.8230675898</v>
       </c>
       <c r="Q24">
-        <v>2.5823874772</v>
+        <v>2.5680675898</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1119248785305634</v>
+        <v>0.1125951472173397</v>
       </c>
       <c r="T24">
-        <v>1.527133453361742</v>
+        <v>1.542613099707614</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.83228137673764</v>
+        <v>6.535225664705568</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -4036,22 +4036,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09587767835735156</v>
+        <v>0.09567364146086364</v>
       </c>
       <c r="C25">
-        <v>28.82960915586537</v>
+        <v>28.55270665127349</v>
       </c>
       <c r="D25">
-        <v>33.39200915586537</v>
+        <v>33.4739066512735</v>
       </c>
       <c r="E25">
-        <v>5.372400000000002</v>
+        <v>5.731200000000002</v>
       </c>
       <c r="F25">
-        <v>8.252400000000002</v>
+        <v>8.611200000000002</v>
       </c>
       <c r="G25">
         <v>3.69</v>
@@ -4072,28 +4072,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M25">
-        <v>0.4481053200000001</v>
+        <v>0.4675881600000001</v>
       </c>
       <c r="N25">
-        <v>2.480364067755102</v>
+        <v>2.460881227755102</v>
       </c>
       <c r="O25">
-        <v>0.657296477955102</v>
+        <v>0.6521335253551021</v>
       </c>
       <c r="P25">
-        <v>1.8230675898</v>
+        <v>1.8087477024</v>
       </c>
       <c r="Q25">
-        <v>2.5680675898</v>
+        <v>2.5537477024</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1125951472173397</v>
+        <v>0.1132830545537679</v>
       </c>
       <c r="T25">
-        <v>1.542613099707614</v>
+        <v>1.558500105167851</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.535225664705568</v>
+        <v>6.262924595342836</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -4118,22 +4118,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09567364146086363</v>
+        <v>0.09565335456437571</v>
       </c>
       <c r="C26">
-        <v>28.5527066512735</v>
+        <v>28.20207148402439</v>
       </c>
       <c r="D26">
-        <v>33.4739066512735</v>
+        <v>33.4820714840244</v>
       </c>
       <c r="E26">
-        <v>5.7312</v>
+        <v>6.090000000000001</v>
       </c>
       <c r="F26">
-        <v>8.6112</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G26">
         <v>3.69</v>
@@ -4154,45 +4154,45 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M26">
-        <v>0.46758816</v>
+        <v>0.4960410000000001</v>
       </c>
       <c r="N26">
-        <v>2.460881227755102</v>
+        <v>2.432428387755102</v>
       </c>
       <c r="O26">
-        <v>0.6521335253551021</v>
+        <v>0.6445935227551021</v>
       </c>
       <c r="P26">
-        <v>1.8087477024</v>
+        <v>1.787834865</v>
       </c>
       <c r="Q26">
-        <v>2.5537477024</v>
+        <v>2.532834865</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1132830545537679</v>
+        <v>0.1139893060858343</v>
       </c>
       <c r="T26">
-        <v>1.558500105167851</v>
+        <v>1.574810764107027</v>
       </c>
       <c r="U26">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.265</v>
       </c>
       <c r="W26">
-        <v>0.0399105</v>
+        <v>0.0406455</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>6.262924595342837</v>
+        <v>5.903684146582846</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -4200,22 +4200,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09565335456437571</v>
+        <v>0.0954566676678878</v>
       </c>
       <c r="C27">
-        <v>28.20207148402439</v>
+        <v>27.92263872381783</v>
       </c>
       <c r="D27">
-        <v>33.4820714840244</v>
+        <v>33.56143872381783</v>
       </c>
       <c r="E27">
-        <v>6.090000000000001</v>
+        <v>6.448800000000001</v>
       </c>
       <c r="F27">
-        <v>8.970000000000001</v>
+        <v>9.328800000000001</v>
       </c>
       <c r="G27">
         <v>3.69</v>
@@ -4236,28 +4236,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M27">
-        <v>0.4960410000000001</v>
+        <v>0.5158826400000001</v>
       </c>
       <c r="N27">
-        <v>2.432428387755102</v>
+        <v>2.412586747755102</v>
       </c>
       <c r="O27">
-        <v>0.6445935227551021</v>
+        <v>0.6393354881551021</v>
       </c>
       <c r="P27">
-        <v>1.787834865</v>
+        <v>1.7732512596</v>
       </c>
       <c r="Q27">
-        <v>2.532834865</v>
+        <v>2.5182512596</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1139893060858343</v>
+        <v>0.1147146454971457</v>
       </c>
       <c r="T27">
-        <v>1.574810764107027</v>
+        <v>1.591562251666182</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.903684146582846</v>
+        <v>5.676619371714275</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -4282,22 +4282,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0954566676678878</v>
+        <v>0.09525998077139985</v>
       </c>
       <c r="C28">
-        <v>27.92263872381783</v>
+        <v>27.64358312820887</v>
       </c>
       <c r="D28">
-        <v>33.56143872381783</v>
+        <v>33.64118312820887</v>
       </c>
       <c r="E28">
-        <v>6.448800000000001</v>
+        <v>6.807600000000002</v>
       </c>
       <c r="F28">
-        <v>9.328800000000001</v>
+        <v>9.687600000000002</v>
       </c>
       <c r="G28">
         <v>3.69</v>
@@ -4318,28 +4318,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M28">
-        <v>0.5158826400000001</v>
+        <v>0.5357242800000001</v>
       </c>
       <c r="N28">
-        <v>2.412586747755102</v>
+        <v>2.392745107755102</v>
       </c>
       <c r="O28">
-        <v>0.6393354881551021</v>
+        <v>0.634077453555102</v>
       </c>
       <c r="P28">
-        <v>1.7732512596</v>
+        <v>1.7586676542</v>
       </c>
       <c r="Q28">
-        <v>2.5182512596</v>
+        <v>2.5036676542</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1147146454971457</v>
+        <v>0.1154598572210957</v>
       </c>
       <c r="T28">
-        <v>1.591562251666182</v>
+        <v>1.60877268408997</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.676619371714275</v>
+        <v>5.466374209798932</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4364,22 +4364,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09525998077139985</v>
+        <v>0.09506329387491194</v>
       </c>
       <c r="C29">
-        <v>27.64358312820887</v>
+        <v>27.36490739211185</v>
       </c>
       <c r="D29">
-        <v>33.64118312820887</v>
+        <v>33.72130739211185</v>
       </c>
       <c r="E29">
-        <v>6.807600000000002</v>
+        <v>7.166400000000002</v>
       </c>
       <c r="F29">
-        <v>9.687600000000002</v>
+        <v>10.0464</v>
       </c>
       <c r="G29">
         <v>3.69</v>
@@ -4400,28 +4400,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M29">
-        <v>0.5357242800000001</v>
+        <v>0.5555659200000002</v>
       </c>
       <c r="N29">
-        <v>2.392745107755102</v>
+        <v>2.372903467755102</v>
       </c>
       <c r="O29">
-        <v>0.634077453555102</v>
+        <v>0.628819418955102</v>
       </c>
       <c r="P29">
-        <v>1.7586676542</v>
+        <v>1.7440840488</v>
       </c>
       <c r="Q29">
-        <v>2.5036676542</v>
+        <v>2.4890840488</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1154598572210957</v>
+        <v>0.116225769270711</v>
       </c>
       <c r="T29">
-        <v>1.60877268408997</v>
+        <v>1.626461184081086</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.466374209798932</v>
+        <v>5.271146559448969</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4446,22 +4446,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09506329387491194</v>
+        <v>0.09486660697842403</v>
       </c>
       <c r="C30">
-        <v>27.36490739211185</v>
+        <v>27.08661423617667</v>
       </c>
       <c r="D30">
-        <v>33.72130739211185</v>
+        <v>33.80181423617667</v>
       </c>
       <c r="E30">
-        <v>7.166400000000002</v>
+        <v>7.525200000000003</v>
       </c>
       <c r="F30">
-        <v>10.0464</v>
+        <v>10.4052</v>
       </c>
       <c r="G30">
         <v>3.69</v>
@@ -4482,28 +4482,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M30">
-        <v>0.5555659200000002</v>
+        <v>0.5754075600000002</v>
       </c>
       <c r="N30">
-        <v>2.372903467755102</v>
+        <v>2.353061827755102</v>
       </c>
       <c r="O30">
-        <v>0.628819418955102</v>
+        <v>0.6235613843551021</v>
       </c>
       <c r="P30">
-        <v>1.7440840488</v>
+        <v>1.7295004434</v>
       </c>
       <c r="Q30">
-        <v>2.4890840488</v>
+        <v>2.4745004434</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.116225769270711</v>
+        <v>0.1170132563076395</v>
       </c>
       <c r="T30">
-        <v>1.626461184081086</v>
+        <v>1.644647951677586</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.271146559448969</v>
+        <v>5.089382884985212</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4528,22 +4528,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09486660697842403</v>
+        <v>0.0946699200819361</v>
       </c>
       <c r="C31">
-        <v>27.08661423617667</v>
+        <v>26.80870640709673</v>
       </c>
       <c r="D31">
-        <v>33.80181423617667</v>
+        <v>33.88270640709673</v>
       </c>
       <c r="E31">
-        <v>7.525200000000001</v>
+        <v>7.884000000000001</v>
       </c>
       <c r="F31">
-        <v>10.4052</v>
+        <v>10.764</v>
       </c>
       <c r="G31">
         <v>3.69</v>
@@ -4564,28 +4564,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M31">
-        <v>0.57540756</v>
+        <v>0.5952492</v>
       </c>
       <c r="N31">
-        <v>2.353061827755102</v>
+        <v>2.333220187755102</v>
       </c>
       <c r="O31">
-        <v>0.6235613843551021</v>
+        <v>0.618303349755102</v>
       </c>
       <c r="P31">
-        <v>1.7295004434</v>
+        <v>1.714916838</v>
       </c>
       <c r="Q31">
-        <v>2.4745004434</v>
+        <v>2.459916838</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1170132563076395</v>
+        <v>0.1178232429741944</v>
       </c>
       <c r="T31">
-        <v>1.644647951677586</v>
+        <v>1.663354341205414</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -4602,7 +4602,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.089382884985213</v>
+        <v>4.919736788819039</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4610,22 +4610,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0946699200819361</v>
+        <v>0.09447323318544817</v>
       </c>
       <c r="C32">
-        <v>26.80870640709673</v>
+        <v>26.53118667792126</v>
       </c>
       <c r="D32">
-        <v>33.88270640709673</v>
+        <v>33.96398667792126</v>
       </c>
       <c r="E32">
-        <v>7.884000000000001</v>
+        <v>8.242800000000003</v>
       </c>
       <c r="F32">
-        <v>10.764</v>
+        <v>11.1228</v>
       </c>
       <c r="G32">
         <v>3.69</v>
@@ -4646,28 +4646,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M32">
-        <v>0.5952492</v>
+        <v>0.6150908400000001</v>
       </c>
       <c r="N32">
-        <v>2.333220187755102</v>
+        <v>2.313378547755102</v>
       </c>
       <c r="O32">
-        <v>0.618303349755102</v>
+        <v>0.6130453151551021</v>
       </c>
       <c r="P32">
-        <v>1.714916838</v>
+        <v>1.7003332326</v>
       </c>
       <c r="Q32">
-        <v>2.459916838</v>
+        <v>2.4453332326</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1178232429741944</v>
+        <v>0.1186567075151423</v>
       </c>
       <c r="T32">
-        <v>1.663354341205414</v>
+        <v>1.682602944922455</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.919736788819039</v>
+        <v>4.76103560208294</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4692,22 +4692,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09447323318544817</v>
+        <v>0.09427654628896026</v>
       </c>
       <c r="C33">
-        <v>26.53118667792126</v>
+        <v>26.25405784837225</v>
       </c>
       <c r="D33">
-        <v>33.96398667792126</v>
+        <v>34.04565784837225</v>
       </c>
       <c r="E33">
-        <v>8.242800000000003</v>
+        <v>8.601600000000001</v>
       </c>
       <c r="F33">
-        <v>11.1228</v>
+        <v>11.4816</v>
       </c>
       <c r="G33">
         <v>3.69</v>
@@ -4728,28 +4728,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M33">
-        <v>0.6150908400000001</v>
+        <v>0.63493248</v>
       </c>
       <c r="N33">
-        <v>2.313378547755102</v>
+        <v>2.293536907755102</v>
       </c>
       <c r="O33">
-        <v>0.6130453151551021</v>
+        <v>0.607787280555102</v>
       </c>
       <c r="P33">
-        <v>1.7003332326</v>
+        <v>1.6857496272</v>
       </c>
       <c r="Q33">
-        <v>2.4453332326</v>
+        <v>2.4307496272</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1186567075151423</v>
+        <v>0.1195146857190592</v>
       </c>
       <c r="T33">
-        <v>1.682602944922455</v>
+        <v>1.702417684042938</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.76103560208294</v>
+        <v>4.612253239517848</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4774,22 +4774,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09427654628896026</v>
+        <v>0.09468623439247234</v>
       </c>
       <c r="C34">
-        <v>26.25405784837225</v>
+        <v>25.72558203602684</v>
       </c>
       <c r="D34">
-        <v>34.04565784837225</v>
+        <v>33.87598203602685</v>
       </c>
       <c r="E34">
-        <v>8.601600000000001</v>
+        <v>8.9604</v>
       </c>
       <c r="F34">
-        <v>11.4816</v>
+        <v>11.8404</v>
       </c>
       <c r="G34">
         <v>3.69</v>
@@ -4810,45 +4810,45 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M34">
-        <v>0.63493248</v>
+        <v>0.6843751200000001</v>
       </c>
       <c r="N34">
-        <v>2.293536907755102</v>
+        <v>2.244094267755102</v>
       </c>
       <c r="O34">
-        <v>0.607787280555102</v>
+        <v>0.5946849809551021</v>
       </c>
       <c r="P34">
-        <v>1.6857496272</v>
+        <v>1.6494092868</v>
       </c>
       <c r="Q34">
-        <v>2.4307496272</v>
+        <v>2.3944092868</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1195146857190592</v>
+        <v>0.1203982752126453</v>
       </c>
       <c r="T34">
-        <v>1.702417684042938</v>
+        <v>1.722823907913286</v>
       </c>
       <c r="U34">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V34">
         <v>0.265</v>
       </c>
       <c r="W34">
-        <v>0.0406455</v>
+        <v>0.042483</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.612253239517848</v>
+        <v>4.279041277472363</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4856,22 +4856,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09468623439247234</v>
+        <v>0.09450792249598441</v>
       </c>
       <c r="C35">
-        <v>25.72558203602684</v>
+        <v>25.44042311281693</v>
       </c>
       <c r="D35">
-        <v>33.87598203602685</v>
+        <v>33.94962311281694</v>
       </c>
       <c r="E35">
-        <v>8.9604</v>
+        <v>9.319200000000002</v>
       </c>
       <c r="F35">
-        <v>11.8404</v>
+        <v>12.1992</v>
       </c>
       <c r="G35">
         <v>3.69</v>
@@ -4892,28 +4892,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M35">
-        <v>0.6843751200000001</v>
+        <v>0.7051137600000001</v>
       </c>
       <c r="N35">
-        <v>2.244094267755102</v>
+        <v>2.223355627755102</v>
       </c>
       <c r="O35">
-        <v>0.5946849809551021</v>
+        <v>0.589189241355102</v>
       </c>
       <c r="P35">
-        <v>1.6494092868</v>
+        <v>1.6341663864</v>
       </c>
       <c r="Q35">
-        <v>2.3944092868</v>
+        <v>2.3791663864</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1203982752126453</v>
+        <v>0.1213086401454309</v>
       </c>
       <c r="T35">
-        <v>1.722823907913286</v>
+        <v>1.743848502203948</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4930,7 +4930,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.279041277472363</v>
+        <v>4.153187122252588</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4938,22 +4938,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09450792249598441</v>
+        <v>0.09432961059949649</v>
       </c>
       <c r="C36">
-        <v>25.44042311281693</v>
+        <v>25.15558505544276</v>
       </c>
       <c r="D36">
-        <v>33.94962311281694</v>
+        <v>34.02358505544277</v>
       </c>
       <c r="E36">
-        <v>9.319200000000002</v>
+        <v>9.678000000000001</v>
       </c>
       <c r="F36">
-        <v>12.1992</v>
+        <v>12.558</v>
       </c>
       <c r="G36">
         <v>3.69</v>
@@ -4974,28 +4974,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M36">
-        <v>0.7051137600000001</v>
+        <v>0.7258524000000002</v>
       </c>
       <c r="N36">
-        <v>2.223355627755102</v>
+        <v>2.202616987755102</v>
       </c>
       <c r="O36">
-        <v>0.589189241355102</v>
+        <v>0.5836935017551019</v>
       </c>
       <c r="P36">
-        <v>1.6341663864</v>
+        <v>1.618923486</v>
       </c>
       <c r="Q36">
-        <v>2.3791663864</v>
+        <v>2.363923486</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1213086401454309</v>
+        <v>0.1222470163069177</v>
       </c>
       <c r="T36">
-        <v>1.743848502203948</v>
+        <v>1.765520007088169</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.153187122252588</v>
+        <v>4.03452463304537</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -5020,22 +5020,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09432961059949649</v>
+        <v>0.09507739870300858</v>
       </c>
       <c r="C37">
-        <v>25.15558505544276</v>
+        <v>24.48874881224079</v>
       </c>
       <c r="D37">
-        <v>34.02358505544277</v>
+        <v>33.71554881224079</v>
       </c>
       <c r="E37">
-        <v>9.678000000000001</v>
+        <v>10.0368</v>
       </c>
       <c r="F37">
-        <v>12.558</v>
+        <v>12.9168</v>
       </c>
       <c r="G37">
         <v>3.69</v>
@@ -5056,45 +5056,45 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M37">
-        <v>0.7258524000000002</v>
+        <v>0.7917998400000001</v>
       </c>
       <c r="N37">
-        <v>2.202616987755102</v>
+        <v>2.136669547755102</v>
       </c>
       <c r="O37">
-        <v>0.5836935017551019</v>
+        <v>0.5662174301551021</v>
       </c>
       <c r="P37">
-        <v>1.618923486</v>
+        <v>1.5704521176</v>
       </c>
       <c r="Q37">
-        <v>2.363923486</v>
+        <v>2.3154521176</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1222470163069177</v>
+        <v>0.1232147167234509</v>
       </c>
       <c r="T37">
-        <v>1.765520007088169</v>
+        <v>1.787868746500021</v>
       </c>
       <c r="U37">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V37">
         <v>0.265</v>
       </c>
       <c r="W37">
-        <v>0.042483</v>
+        <v>0.0450555</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.03452463304537</v>
+        <v>3.698497069354171</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -5102,22 +5102,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09507739870300858</v>
+        <v>0.09492481180652067</v>
       </c>
       <c r="C38">
-        <v>24.48874881224079</v>
+        <v>24.19235012456639</v>
       </c>
       <c r="D38">
-        <v>33.71554881224079</v>
+        <v>33.7779501245664</v>
       </c>
       <c r="E38">
-        <v>10.0368</v>
+        <v>10.3956</v>
       </c>
       <c r="F38">
-        <v>12.9168</v>
+        <v>13.2756</v>
       </c>
       <c r="G38">
         <v>3.69</v>
@@ -5138,28 +5138,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M38">
-        <v>0.79179984</v>
+        <v>0.8137942800000001</v>
       </c>
       <c r="N38">
-        <v>2.136669547755102</v>
+        <v>2.114675107755102</v>
       </c>
       <c r="O38">
-        <v>0.5662174301551021</v>
+        <v>0.560388903555102</v>
       </c>
       <c r="P38">
-        <v>1.5704521176</v>
+        <v>1.5542862042</v>
       </c>
       <c r="Q38">
-        <v>2.3154521176</v>
+        <v>2.2992862042</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1232147167234509</v>
+        <v>0.124213137788128</v>
       </c>
       <c r="T38">
-        <v>1.787868746500021</v>
+        <v>1.810926969702726</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.698497069354171</v>
+        <v>3.598537689101356</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -5184,22 +5184,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09492481180652067</v>
+        <v>0.09477222491003273</v>
       </c>
       <c r="C39">
-        <v>24.19235012456639</v>
+        <v>23.89618285202368</v>
       </c>
       <c r="D39">
-        <v>33.7779501245664</v>
+        <v>33.84058285202369</v>
       </c>
       <c r="E39">
-        <v>10.3956</v>
+        <v>10.7544</v>
       </c>
       <c r="F39">
-        <v>13.2756</v>
+        <v>13.6344</v>
       </c>
       <c r="G39">
         <v>3.69</v>
@@ -5220,28 +5220,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M39">
-        <v>0.8137942800000001</v>
+        <v>0.83578872</v>
       </c>
       <c r="N39">
-        <v>2.114675107755102</v>
+        <v>2.092680667755102</v>
       </c>
       <c r="O39">
-        <v>0.560388903555102</v>
+        <v>0.5545603769551021</v>
       </c>
       <c r="P39">
-        <v>1.5542862042</v>
+        <v>1.5381202908</v>
       </c>
       <c r="Q39">
-        <v>2.2992862042</v>
+        <v>2.2831202908</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.124213137788128</v>
+        <v>0.1252437659839238</v>
       </c>
       <c r="T39">
-        <v>1.810926969702726</v>
+        <v>1.834729006557131</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -5258,7 +5258,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.598537689101356</v>
+        <v>3.503839328861847</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -5266,22 +5266,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09477222491003273</v>
+        <v>0.09542225801354483</v>
       </c>
       <c r="C40">
-        <v>23.89618285202368</v>
+        <v>23.27216242034596</v>
       </c>
       <c r="D40">
-        <v>33.84058285202369</v>
+        <v>33.57536242034596</v>
       </c>
       <c r="E40">
-        <v>10.7544</v>
+        <v>11.1132</v>
       </c>
       <c r="F40">
-        <v>13.6344</v>
+        <v>13.9932</v>
       </c>
       <c r="G40">
         <v>3.69</v>
@@ -5302,45 +5302,45 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M40">
-        <v>0.83578872</v>
+        <v>0.8969641200000001</v>
       </c>
       <c r="N40">
-        <v>2.092680667755102</v>
+        <v>2.031505267755102</v>
       </c>
       <c r="O40">
-        <v>0.5545603769551021</v>
+        <v>0.538348895955102</v>
       </c>
       <c r="P40">
-        <v>1.5381202908</v>
+        <v>1.4931563718</v>
       </c>
       <c r="Q40">
-        <v>2.2831202908</v>
+        <v>2.2381563718</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1252437659839238</v>
+        <v>0.1263081852681063</v>
       </c>
       <c r="T40">
-        <v>1.834729006557131</v>
+        <v>1.8593114380625</v>
       </c>
       <c r="U40">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V40">
         <v>0.265</v>
       </c>
       <c r="W40">
-        <v>0.0450555</v>
+        <v>0.0471135</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.503839328861847</v>
+        <v>3.264867927777425</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5348,22 +5348,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09542225801354483</v>
+        <v>0.0952902511170569</v>
       </c>
       <c r="C41">
-        <v>23.27216242034596</v>
+        <v>22.96688570616</v>
       </c>
       <c r="D41">
-        <v>33.57536242034596</v>
+        <v>33.62888570616001</v>
       </c>
       <c r="E41">
-        <v>11.1132</v>
+        <v>11.472</v>
       </c>
       <c r="F41">
-        <v>13.9932</v>
+        <v>14.352</v>
       </c>
       <c r="G41">
         <v>3.69</v>
@@ -5384,28 +5384,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M41">
-        <v>0.8969641200000001</v>
+        <v>0.9199632000000002</v>
       </c>
       <c r="N41">
-        <v>2.031505267755102</v>
+        <v>2.008506187755102</v>
       </c>
       <c r="O41">
-        <v>0.538348895955102</v>
+        <v>0.5322541397551021</v>
       </c>
       <c r="P41">
-        <v>1.4931563718</v>
+        <v>1.476252048</v>
       </c>
       <c r="Q41">
-        <v>2.2381563718</v>
+        <v>2.221252048</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1263081852681063</v>
+        <v>0.1274080851950948</v>
       </c>
       <c r="T41">
-        <v>1.8593114380625</v>
+        <v>1.884713283951382</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.264867927777425</v>
+        <v>3.183246229582989</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5430,22 +5430,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0952902511170569</v>
+        <v>0.09515824422056898</v>
       </c>
       <c r="C42">
-        <v>22.96688570616</v>
+        <v>22.66177990993071</v>
       </c>
       <c r="D42">
-        <v>33.62888570616001</v>
+        <v>33.68257990993072</v>
       </c>
       <c r="E42">
-        <v>11.472</v>
+        <v>11.8308</v>
       </c>
       <c r="F42">
-        <v>14.352</v>
+        <v>14.7108</v>
       </c>
       <c r="G42">
         <v>3.69</v>
@@ -5466,28 +5466,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M42">
-        <v>0.9199632000000002</v>
+        <v>0.9429622800000003</v>
       </c>
       <c r="N42">
-        <v>2.008506187755102</v>
+        <v>1.985507107755102</v>
       </c>
       <c r="O42">
-        <v>0.5322541397551021</v>
+        <v>0.5261593835551021</v>
       </c>
       <c r="P42">
-        <v>1.476252048</v>
+        <v>1.4593477242</v>
       </c>
       <c r="Q42">
-        <v>2.221252048</v>
+        <v>2.2043477242</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1274080851950948</v>
+        <v>0.1285452698653712</v>
       </c>
       <c r="T42">
-        <v>1.884713283951382</v>
+        <v>1.91097620936192</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.183246229582989</v>
+        <v>3.105606077641941</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5512,22 +5512,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09515824422056898</v>
+        <v>0.09502623732408107</v>
       </c>
       <c r="C43">
-        <v>22.66177990993071</v>
+        <v>22.35684585166566</v>
       </c>
       <c r="D43">
-        <v>33.68257990993072</v>
+        <v>33.73644585166566</v>
       </c>
       <c r="E43">
-        <v>11.8308</v>
+        <v>12.1896</v>
       </c>
       <c r="F43">
-        <v>14.7108</v>
+        <v>15.0696</v>
       </c>
       <c r="G43">
         <v>3.69</v>
@@ -5548,28 +5548,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M43">
-        <v>0.9429622800000003</v>
+        <v>0.9659613600000002</v>
       </c>
       <c r="N43">
-        <v>1.985507107755102</v>
+        <v>1.962508027755102</v>
       </c>
       <c r="O43">
-        <v>0.5261593835551021</v>
+        <v>0.5200646273551021</v>
       </c>
       <c r="P43">
-        <v>1.4593477242</v>
+        <v>1.4424434004</v>
       </c>
       <c r="Q43">
-        <v>2.2043477242</v>
+        <v>2.1874434004</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1285452698653712</v>
+        <v>0.1297216678001398</v>
       </c>
       <c r="T43">
-        <v>1.91097620936192</v>
+        <v>1.938144752890064</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.105606077641941</v>
+        <v>3.031663075793323</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5594,22 +5594,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09502623732408108</v>
+        <v>0.09735942042759314</v>
       </c>
       <c r="C44">
-        <v>22.35684585166565</v>
+        <v>21.07067156316581</v>
       </c>
       <c r="D44">
-        <v>33.73644585166566</v>
+        <v>32.80907156316582</v>
       </c>
       <c r="E44">
-        <v>12.1896</v>
+        <v>12.5484</v>
       </c>
       <c r="F44">
-        <v>15.0696</v>
+        <v>15.4284</v>
       </c>
       <c r="G44">
         <v>3.69</v>
@@ -5630,45 +5630,45 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M44">
-        <v>0.9659613600000001</v>
+        <v>1.10930196</v>
       </c>
       <c r="N44">
-        <v>1.962508027755102</v>
+        <v>1.819167427755102</v>
       </c>
       <c r="O44">
-        <v>0.5200646273551021</v>
+        <v>0.482079368355102</v>
       </c>
       <c r="P44">
-        <v>1.4424434004</v>
+        <v>1.3370880594</v>
       </c>
       <c r="Q44">
-        <v>2.1874434004</v>
+        <v>2.0820880594</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1297216678001398</v>
+        <v>0.1309393428554265</v>
       </c>
       <c r="T44">
-        <v>1.938144752890064</v>
+        <v>1.966266578647265</v>
       </c>
       <c r="U44">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V44">
         <v>0.265</v>
       </c>
       <c r="W44">
-        <v>0.0471135</v>
+        <v>0.0528465</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.031663075793323</v>
+        <v>2.639920863166149</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5676,22 +5676,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09735942042759314</v>
+        <v>0.09728474353110524</v>
       </c>
       <c r="C45">
-        <v>21.07067156316581</v>
+        <v>20.74076301529789</v>
       </c>
       <c r="D45">
-        <v>32.80907156316582</v>
+        <v>32.83796301529789</v>
       </c>
       <c r="E45">
-        <v>12.5484</v>
+        <v>12.9072</v>
       </c>
       <c r="F45">
-        <v>15.4284</v>
+        <v>15.7872</v>
       </c>
       <c r="G45">
         <v>3.69</v>
@@ -5712,28 +5712,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M45">
-        <v>1.10930196</v>
+        <v>1.13509968</v>
       </c>
       <c r="N45">
-        <v>1.819167427755102</v>
+        <v>1.793369707755102</v>
       </c>
       <c r="O45">
-        <v>0.482079368355102</v>
+        <v>0.475242972555102</v>
       </c>
       <c r="P45">
-        <v>1.3370880594</v>
+        <v>1.3181267352</v>
       </c>
       <c r="Q45">
-        <v>2.0820880594</v>
+        <v>2.0631267352</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1309393428554265</v>
+        <v>0.1322005063055451</v>
       </c>
       <c r="T45">
-        <v>1.966266578647265</v>
+        <v>1.995392755324366</v>
       </c>
       <c r="U45">
         <v>0.07190000000000001</v>
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.639920863166149</v>
+        <v>2.579922661730556</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5758,22 +5758,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09728474353110524</v>
+        <v>0.09721006663461731</v>
       </c>
       <c r="C46">
-        <v>20.74076301529789</v>
+        <v>20.41090539552149</v>
       </c>
       <c r="D46">
-        <v>32.83796301529789</v>
+        <v>32.86690539552149</v>
       </c>
       <c r="E46">
-        <v>12.9072</v>
+        <v>13.266</v>
       </c>
       <c r="F46">
-        <v>15.7872</v>
+        <v>16.146</v>
       </c>
       <c r="G46">
         <v>3.69</v>
@@ -5794,28 +5794,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M46">
-        <v>1.13509968</v>
+        <v>1.1608974</v>
       </c>
       <c r="N46">
-        <v>1.793369707755102</v>
+        <v>1.767571987755102</v>
       </c>
       <c r="O46">
-        <v>0.475242972555102</v>
+        <v>0.4684065767551021</v>
       </c>
       <c r="P46">
-        <v>1.3181267352</v>
+        <v>1.299165411</v>
       </c>
       <c r="Q46">
-        <v>2.0631267352</v>
+        <v>2.044165411</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1322005063055451</v>
+        <v>0.1335075302447587</v>
       </c>
       <c r="T46">
-        <v>1.995392755324366</v>
+        <v>2.025578065698816</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.579922661730556</v>
+        <v>2.522591047025432</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5840,22 +5840,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09721006663461731</v>
+        <v>0.0984539797381294</v>
       </c>
       <c r="C47">
-        <v>20.41090539552149</v>
+        <v>19.57656105838113</v>
       </c>
       <c r="D47">
-        <v>32.86690539552149</v>
+        <v>32.39136105838114</v>
       </c>
       <c r="E47">
-        <v>13.266</v>
+        <v>13.6248</v>
       </c>
       <c r="F47">
-        <v>16.146</v>
+        <v>16.5048</v>
       </c>
       <c r="G47">
         <v>3.69</v>
@@ -5876,45 +5876,45 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M47">
-        <v>1.1608974</v>
+        <v>1.25106384</v>
       </c>
       <c r="N47">
-        <v>1.767571987755102</v>
+        <v>1.677405547755102</v>
       </c>
       <c r="O47">
-        <v>0.4684065767551021</v>
+        <v>0.444512470155102</v>
       </c>
       <c r="P47">
-        <v>1.299165411</v>
+        <v>1.2328930776</v>
       </c>
       <c r="Q47">
-        <v>2.044165411</v>
+        <v>1.9778930776</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1335075302447587</v>
+        <v>0.1348629624780174</v>
       </c>
       <c r="T47">
-        <v>2.025578065698816</v>
+        <v>2.056881350531579</v>
       </c>
       <c r="U47">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V47">
         <v>0.265</v>
       </c>
       <c r="W47">
-        <v>0.0528465</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.522591047025432</v>
+        <v>2.340783335049554</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5922,22 +5922,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0984539797381294</v>
+        <v>0.09840796784164146</v>
       </c>
       <c r="C48">
-        <v>19.57656105838113</v>
+        <v>19.23510604554126</v>
       </c>
       <c r="D48">
-        <v>32.39136105838114</v>
+        <v>32.40870604554127</v>
       </c>
       <c r="E48">
-        <v>13.6248</v>
+        <v>13.9836</v>
       </c>
       <c r="F48">
-        <v>16.5048</v>
+        <v>16.8636</v>
       </c>
       <c r="G48">
         <v>3.69</v>
@@ -5958,28 +5958,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M48">
-        <v>1.25106384</v>
+        <v>1.27826088</v>
       </c>
       <c r="N48">
-        <v>1.677405547755102</v>
+        <v>1.650208507755102</v>
       </c>
       <c r="O48">
-        <v>0.444512470155102</v>
+        <v>0.437305254555102</v>
       </c>
       <c r="P48">
-        <v>1.2328930776</v>
+        <v>1.2129032532</v>
       </c>
       <c r="Q48">
-        <v>1.9778930776</v>
+        <v>1.9579032532</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1348629624780174</v>
+        <v>0.1362695430974367</v>
       </c>
       <c r="T48">
-        <v>2.056881350531579</v>
+        <v>2.089365891395767</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5996,7 +5996,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.340783335049554</v>
+        <v>2.290979434303819</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -6004,22 +6004,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09840796784164146</v>
+        <v>0.09836195594515355</v>
       </c>
       <c r="C49">
-        <v>19.23510604554126</v>
+        <v>18.89366961850667</v>
       </c>
       <c r="D49">
-        <v>32.40870604554127</v>
+        <v>32.42606961850668</v>
       </c>
       <c r="E49">
-        <v>13.9836</v>
+        <v>14.3424</v>
       </c>
       <c r="F49">
-        <v>16.8636</v>
+        <v>17.2224</v>
       </c>
       <c r="G49">
         <v>3.69</v>
@@ -6040,28 +6040,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M49">
-        <v>1.27826088</v>
+        <v>1.30545792</v>
       </c>
       <c r="N49">
-        <v>1.650208507755102</v>
+        <v>1.623011467755102</v>
       </c>
       <c r="O49">
-        <v>0.437305254555102</v>
+        <v>0.4300980389551019</v>
       </c>
       <c r="P49">
-        <v>1.2129032532</v>
+        <v>1.1929134288</v>
       </c>
       <c r="Q49">
-        <v>1.9579032532</v>
+        <v>1.9379134288</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1362695430974367</v>
+        <v>0.1377302229714491</v>
       </c>
       <c r="T49">
-        <v>2.089365891395767</v>
+        <v>2.123099837677809</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.290979434303819</v>
+        <v>2.243250696089155</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -6086,22 +6086,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09836195594515355</v>
+        <v>0.09831594404866562</v>
       </c>
       <c r="C50">
-        <v>18.89366961850668</v>
+        <v>18.55225180716648</v>
       </c>
       <c r="D50">
-        <v>32.42606961850668</v>
+        <v>32.44345180716649</v>
       </c>
       <c r="E50">
-        <v>14.3424</v>
+        <v>14.7012</v>
       </c>
       <c r="F50">
-        <v>17.2224</v>
+        <v>17.5812</v>
       </c>
       <c r="G50">
         <v>3.69</v>
@@ -6122,28 +6122,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M50">
-        <v>1.30545792</v>
+        <v>1.33265496</v>
       </c>
       <c r="N50">
-        <v>1.623011467755102</v>
+        <v>1.595814427755102</v>
       </c>
       <c r="O50">
-        <v>0.4300980389551021</v>
+        <v>0.422890823355102</v>
       </c>
       <c r="P50">
-        <v>1.1929134288</v>
+        <v>1.1729236044</v>
       </c>
       <c r="Q50">
-        <v>1.9379134288</v>
+        <v>1.9179236044</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1377302229714491</v>
+        <v>0.1392481844091483</v>
       </c>
       <c r="T50">
-        <v>2.123099837677809</v>
+        <v>2.158156683814048</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.243250696089156</v>
+        <v>2.197470069638356</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -6168,22 +6168,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09831594404866562</v>
+        <v>0.09826993215217769</v>
       </c>
       <c r="C51">
-        <v>18.55225180716648</v>
+        <v>18.2108526414739</v>
       </c>
       <c r="D51">
-        <v>32.44345180716649</v>
+        <v>32.4608526414739</v>
       </c>
       <c r="E51">
-        <v>14.7012</v>
+        <v>15.06</v>
       </c>
       <c r="F51">
-        <v>17.5812</v>
+        <v>17.94</v>
       </c>
       <c r="G51">
         <v>3.69</v>
@@ -6204,28 +6204,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M51">
-        <v>1.33265496</v>
+        <v>1.359852</v>
       </c>
       <c r="N51">
-        <v>1.595814427755102</v>
+        <v>1.568617387755102</v>
       </c>
       <c r="O51">
-        <v>0.422890823355102</v>
+        <v>0.415683607755102</v>
       </c>
       <c r="P51">
-        <v>1.1729236044</v>
+        <v>1.15293378</v>
       </c>
       <c r="Q51">
-        <v>1.9179236044</v>
+        <v>1.89793378</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1392481844091483</v>
+        <v>0.1408268643043554</v>
       </c>
       <c r="T51">
-        <v>2.158156683814048</v>
+        <v>2.194615803795736</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.197470069638356</v>
+        <v>2.15352066824559</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -6250,22 +6250,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09826993215217769</v>
+        <v>0.09822392025568977</v>
       </c>
       <c r="C52">
-        <v>18.2108526414739</v>
+        <v>17.86947215144643</v>
       </c>
       <c r="D52">
-        <v>32.4608526414739</v>
+        <v>32.47827215144643</v>
       </c>
       <c r="E52">
-        <v>15.06</v>
+        <v>15.4188</v>
       </c>
       <c r="F52">
-        <v>17.94</v>
+        <v>18.2988</v>
       </c>
       <c r="G52">
         <v>3.69</v>
@@ -6286,28 +6286,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M52">
-        <v>1.359852</v>
+        <v>1.38704904</v>
       </c>
       <c r="N52">
-        <v>1.568617387755102</v>
+        <v>1.541420347755102</v>
       </c>
       <c r="O52">
-        <v>0.415683607755102</v>
+        <v>0.408476392155102</v>
       </c>
       <c r="P52">
-        <v>1.15293378</v>
+        <v>1.1329439556</v>
       </c>
       <c r="Q52">
-        <v>1.89793378</v>
+        <v>1.8779439556</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1408268643043554</v>
+        <v>0.1424699801136526</v>
       </c>
       <c r="T52">
-        <v>2.194615803795736</v>
+        <v>2.232563051123617</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -6324,7 +6324,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.15352066824559</v>
+        <v>2.111294772789794</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -6332,22 +6332,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09822392025568977</v>
+        <v>0.09817790835920187</v>
       </c>
       <c r="C53">
-        <v>17.86947215144643</v>
+        <v>17.52811036716605</v>
       </c>
       <c r="D53">
-        <v>32.47827215144643</v>
+        <v>32.49571036716605</v>
       </c>
       <c r="E53">
-        <v>15.4188</v>
+        <v>15.7776</v>
       </c>
       <c r="F53">
-        <v>18.2988</v>
+        <v>18.6576</v>
       </c>
       <c r="G53">
         <v>3.69</v>
@@ -6368,28 +6368,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M53">
-        <v>1.38704904</v>
+        <v>1.41424608</v>
       </c>
       <c r="N53">
-        <v>1.541420347755102</v>
+        <v>1.514223307755102</v>
       </c>
       <c r="O53">
-        <v>0.408476392155102</v>
+        <v>0.401269176555102</v>
       </c>
       <c r="P53">
-        <v>1.1329439556</v>
+        <v>1.1129541312</v>
       </c>
       <c r="Q53">
-        <v>1.8779439556</v>
+        <v>1.8579541312</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1424699801136526</v>
+        <v>0.1441815590816705</v>
       </c>
       <c r="T53">
-        <v>2.232563051123617</v>
+        <v>2.272091433756826</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -6406,7 +6406,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.111294772789794</v>
+        <v>2.070692950236144</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6414,22 +6414,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09817790835920187</v>
+        <v>0.09813189646271393</v>
       </c>
       <c r="C54">
-        <v>17.52811036716605</v>
+        <v>17.18676731877943</v>
       </c>
       <c r="D54">
-        <v>32.49571036716605</v>
+        <v>32.51316731877943</v>
       </c>
       <c r="E54">
-        <v>15.7776</v>
+        <v>16.1364</v>
       </c>
       <c r="F54">
-        <v>18.6576</v>
+        <v>19.0164</v>
       </c>
       <c r="G54">
         <v>3.69</v>
@@ -6450,28 +6450,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M54">
-        <v>1.41424608</v>
+        <v>1.44144312</v>
       </c>
       <c r="N54">
-        <v>1.514223307755102</v>
+        <v>1.487026267755102</v>
       </c>
       <c r="O54">
-        <v>0.401269176555102</v>
+        <v>0.394061960955102</v>
       </c>
       <c r="P54">
-        <v>1.1129541312</v>
+        <v>1.0929643068</v>
       </c>
       <c r="Q54">
-        <v>1.8579541312</v>
+        <v>1.8379643068</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1441815590816705</v>
+        <v>0.1459659711972637</v>
       </c>
       <c r="T54">
-        <v>2.272091433756826</v>
+        <v>2.31330187522549</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.070692950236144</v>
+        <v>2.031623271929802</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6496,22 +6496,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09813189646271393</v>
+        <v>0.103721864566226</v>
       </c>
       <c r="C55">
-        <v>17.18676731877943</v>
+        <v>14.83599584728062</v>
       </c>
       <c r="D55">
-        <v>32.51316731877943</v>
+        <v>30.52119584728062</v>
       </c>
       <c r="E55">
-        <v>16.1364</v>
+        <v>16.4952</v>
       </c>
       <c r="F55">
-        <v>19.0164</v>
+        <v>19.3752</v>
       </c>
       <c r="G55">
         <v>3.69</v>
@@ -6532,45 +6532,45 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M55">
-        <v>1.44144312</v>
+        <v>1.743768</v>
       </c>
       <c r="N55">
-        <v>1.487026267755102</v>
+        <v>1.184701387755102</v>
       </c>
       <c r="O55">
-        <v>0.394061960955102</v>
+        <v>0.313945867755102</v>
       </c>
       <c r="P55">
-        <v>1.0929643068</v>
+        <v>0.8707555199999999</v>
       </c>
       <c r="Q55">
-        <v>1.8379643068</v>
+        <v>1.61575552</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1459659711972637</v>
+        <v>0.1478279664483174</v>
       </c>
       <c r="T55">
-        <v>2.31330187522549</v>
+        <v>2.356304075018878</v>
       </c>
       <c r="U55">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V55">
         <v>0.265</v>
       </c>
       <c r="W55">
-        <v>0.05571300000000001</v>
+        <v>0.06615</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.031623271929802</v>
+        <v>1.679391632232672</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6578,22 +6578,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.103721864566226</v>
+        <v>0.1037802226697381</v>
       </c>
       <c r="C56">
-        <v>14.83599584728062</v>
+        <v>14.4576866441537</v>
       </c>
       <c r="D56">
-        <v>30.52119584728062</v>
+        <v>30.5016866441537</v>
       </c>
       <c r="E56">
-        <v>16.4952</v>
+        <v>16.854</v>
       </c>
       <c r="F56">
-        <v>19.3752</v>
+        <v>19.734</v>
       </c>
       <c r="G56">
         <v>3.69</v>
@@ -6614,28 +6614,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M56">
-        <v>1.743768</v>
+        <v>1.77606</v>
       </c>
       <c r="N56">
-        <v>1.184701387755102</v>
+        <v>1.152409387755102</v>
       </c>
       <c r="O56">
-        <v>0.313945867755102</v>
+        <v>0.305388487755102</v>
       </c>
       <c r="P56">
-        <v>0.8707555199999999</v>
+        <v>0.8470208999999997</v>
       </c>
       <c r="Q56">
-        <v>1.61575552</v>
+        <v>1.5920209</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1478279664483174</v>
+        <v>0.1497727170438624</v>
       </c>
       <c r="T56">
-        <v>2.356304075018878</v>
+        <v>2.401217483691974</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.679391632232672</v>
+        <v>1.648857238919351</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6660,22 +6660,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1037802226697381</v>
+        <v>0.1038385807732502</v>
       </c>
       <c r="C57">
-        <v>14.4576866441537</v>
+        <v>14.07940236573011</v>
       </c>
       <c r="D57">
-        <v>30.5016866441537</v>
+        <v>30.48220236573012</v>
       </c>
       <c r="E57">
-        <v>16.854</v>
+        <v>17.2128</v>
       </c>
       <c r="F57">
-        <v>19.734</v>
+        <v>20.0928</v>
       </c>
       <c r="G57">
         <v>3.69</v>
@@ -6696,28 +6696,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M57">
-        <v>1.77606</v>
+        <v>1.808352</v>
       </c>
       <c r="N57">
-        <v>1.152409387755102</v>
+        <v>1.120117387755102</v>
       </c>
       <c r="O57">
-        <v>0.305388487755102</v>
+        <v>0.296831107755102</v>
       </c>
       <c r="P57">
-        <v>0.8470208999999997</v>
+        <v>0.8232862799999998</v>
       </c>
       <c r="Q57">
-        <v>1.5920209</v>
+        <v>1.56828628</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1497727170438624</v>
+        <v>0.1518058653937504</v>
       </c>
       <c r="T57">
-        <v>2.401217483691974</v>
+        <v>2.448172410941118</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.648857238919351</v>
+        <v>1.619413359652933</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6742,22 +6742,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1038385807732502</v>
+        <v>0.1038969388767623</v>
       </c>
       <c r="C58">
-        <v>14.07940236573011</v>
+        <v>13.70114296427515</v>
       </c>
       <c r="D58">
-        <v>30.48220236573012</v>
+        <v>30.46274296427515</v>
       </c>
       <c r="E58">
-        <v>17.2128</v>
+        <v>17.5716</v>
       </c>
       <c r="F58">
-        <v>20.0928</v>
+        <v>20.4516</v>
       </c>
       <c r="G58">
         <v>3.69</v>
@@ -6778,28 +6778,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M58">
-        <v>1.808352</v>
+        <v>1.840644</v>
       </c>
       <c r="N58">
-        <v>1.120117387755102</v>
+        <v>1.087825387755102</v>
       </c>
       <c r="O58">
-        <v>0.296831107755102</v>
+        <v>0.288273727755102</v>
       </c>
       <c r="P58">
-        <v>0.8232862799999998</v>
+        <v>0.7995516599999999</v>
       </c>
       <c r="Q58">
-        <v>1.56828628</v>
+        <v>1.54455166</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1518058653937504</v>
+        <v>0.153933578783168</v>
       </c>
       <c r="T58">
-        <v>2.448172410941118</v>
+        <v>2.497311288294874</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.619413359652933</v>
+        <v>1.591002598957268</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6824,22 +6824,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1038969388767623</v>
+        <v>0.1039552969802743</v>
       </c>
       <c r="C59">
-        <v>13.70114296427515</v>
+        <v>13.3229083921759</v>
       </c>
       <c r="D59">
-        <v>30.46274296427515</v>
+        <v>30.44330839217591</v>
       </c>
       <c r="E59">
-        <v>17.5716</v>
+        <v>17.93040000000001</v>
       </c>
       <c r="F59">
-        <v>20.4516</v>
+        <v>20.8104</v>
       </c>
       <c r="G59">
         <v>3.69</v>
@@ -6860,28 +6860,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M59">
-        <v>1.840644</v>
+        <v>1.872936</v>
       </c>
       <c r="N59">
-        <v>1.087825387755102</v>
+        <v>1.055533387755102</v>
       </c>
       <c r="O59">
-        <v>0.288273727755102</v>
+        <v>0.279716347755102</v>
       </c>
       <c r="P59">
-        <v>0.7995516599999999</v>
+        <v>0.7758170399999997</v>
       </c>
       <c r="Q59">
-        <v>1.54455166</v>
+        <v>1.52081704</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.153933578783168</v>
+        <v>0.1561626118577961</v>
       </c>
       <c r="T59">
-        <v>2.497311288294874</v>
+        <v>2.548790112189286</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6898,7 +6898,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.591002598957268</v>
+        <v>1.563571519664901</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6906,22 +6906,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1039552969802743</v>
+        <v>0.1040136550837864</v>
       </c>
       <c r="C60">
-        <v>13.32290839217591</v>
+        <v>12.94469860194091</v>
       </c>
       <c r="D60">
-        <v>30.44330839217591</v>
+        <v>30.42389860194091</v>
       </c>
       <c r="E60">
-        <v>17.9304</v>
+        <v>18.2892</v>
       </c>
       <c r="F60">
-        <v>20.8104</v>
+        <v>21.1692</v>
       </c>
       <c r="G60">
         <v>3.69</v>
@@ -6942,28 +6942,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M60">
-        <v>1.872936</v>
+        <v>1.905228</v>
       </c>
       <c r="N60">
-        <v>1.055533387755102</v>
+        <v>1.023241387755102</v>
       </c>
       <c r="O60">
-        <v>0.279716347755102</v>
+        <v>0.2711589677551021</v>
       </c>
       <c r="P60">
-        <v>0.7758170399999998</v>
+        <v>0.75208242</v>
       </c>
       <c r="Q60">
-        <v>1.52081704</v>
+        <v>1.49708242</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.156162611857796</v>
+        <v>0.1585003782531376</v>
       </c>
       <c r="T60">
-        <v>2.548790112189284</v>
+        <v>2.602780098224887</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.563571519664901</v>
+        <v>1.537070307467191</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6988,22 +6988,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1040136550837864</v>
+        <v>0.1040720131872985</v>
       </c>
       <c r="C61">
-        <v>12.94469860194091</v>
+        <v>12.56651354619969</v>
       </c>
       <c r="D61">
-        <v>30.42389860194091</v>
+        <v>30.40451354619969</v>
       </c>
       <c r="E61">
-        <v>18.2892</v>
+        <v>18.648</v>
       </c>
       <c r="F61">
-        <v>21.1692</v>
+        <v>21.528</v>
       </c>
       <c r="G61">
         <v>3.69</v>
@@ -7024,28 +7024,28 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M61">
-        <v>1.905228</v>
+        <v>1.93752</v>
       </c>
       <c r="N61">
-        <v>1.023241387755102</v>
+        <v>0.9909493877551019</v>
       </c>
       <c r="O61">
-        <v>0.2711589677551021</v>
+        <v>0.262601587755102</v>
       </c>
       <c r="P61">
-        <v>0.75208242</v>
+        <v>0.7283477999999999</v>
       </c>
       <c r="Q61">
-        <v>1.49708242</v>
+        <v>1.4733478</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1585003782531376</v>
+        <v>0.1609550329682462</v>
       </c>
       <c r="T61">
-        <v>2.602780098224887</v>
+        <v>2.659469583562269</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.537070307467191</v>
+        <v>1.511452469009405</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -7070,22 +7070,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1040720131872985</v>
+        <v>0.1324819866945163</v>
       </c>
       <c r="C62">
-        <v>12.56651354619969</v>
+        <v>5.009461748813656</v>
       </c>
       <c r="D62">
-        <v>30.40451354619969</v>
+        <v>23.20626174881366</v>
       </c>
       <c r="E62">
-        <v>18.648</v>
+        <v>19.0068</v>
       </c>
       <c r="F62">
-        <v>21.528</v>
+        <v>21.8868</v>
       </c>
       <c r="G62">
         <v>3.69</v>
@@ -7106,45 +7106,45 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M62">
-        <v>1.93752</v>
+        <v>3.212982240000001</v>
       </c>
       <c r="N62">
-        <v>0.9909493877551019</v>
+        <v>-0.2845128522448985</v>
       </c>
       <c r="O62">
-        <v>0.262601587755102</v>
+        <v>-0.07539590584489811</v>
       </c>
       <c r="P62">
-        <v>0.7283477999999999</v>
+        <v>-0.2091169464000004</v>
       </c>
       <c r="Q62">
-        <v>1.4733478</v>
+        <v>0.5358830535999995</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1609550329682462</v>
+        <v>0.1655458244257458</v>
       </c>
       <c r="T62">
-        <v>2.659469583562269</v>
+        <v>2.765492480964106</v>
       </c>
       <c r="U62">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.265</v>
+        <v>0.2415339798937395</v>
       </c>
       <c r="W62">
-        <v>0.06615</v>
+        <v>0.1113428117515991</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.511452469009405</v>
+        <v>0.9114489807310923</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -7152,22 +7152,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1324819866945163</v>
+        <v>0.1334919866945163</v>
       </c>
       <c r="C63">
-        <v>5.009461748813656</v>
+        <v>4.456972864887273</v>
       </c>
       <c r="D63">
-        <v>23.20626174881366</v>
+        <v>23.01257286488728</v>
       </c>
       <c r="E63">
-        <v>19.0068</v>
+        <v>19.3656</v>
       </c>
       <c r="F63">
-        <v>21.8868</v>
+        <v>22.2456</v>
       </c>
       <c r="G63">
         <v>3.69</v>
@@ -7188,37 +7188,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M63">
-        <v>3.212982240000001</v>
+        <v>3.265654080000001</v>
       </c>
       <c r="N63">
-        <v>-0.2845128522448985</v>
+        <v>-0.3371846922448989</v>
       </c>
       <c r="O63">
-        <v>-0.07539590584489811</v>
+        <v>-0.08935394344489821</v>
       </c>
       <c r="P63">
-        <v>-0.2091169464000004</v>
+        <v>-0.2478307488000007</v>
       </c>
       <c r="Q63">
-        <v>0.5358830535999995</v>
+        <v>0.4971692511999993</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1655458244257458</v>
+        <v>0.1686970303316865</v>
       </c>
       <c r="T63">
-        <v>2.765492480964106</v>
+        <v>2.838268598884214</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2415339798937395</v>
+        <v>0.2376382705406146</v>
       </c>
       <c r="W63">
-        <v>0.1113428117515991</v>
+        <v>0.1119147018846378</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.9114489807310923</v>
+        <v>0.8967481907193003</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -7234,22 +7234,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1334919866945163</v>
+        <v>0.1345019866945163</v>
       </c>
       <c r="C64">
-        <v>4.456972864887273</v>
+        <v>3.907690430781702</v>
       </c>
       <c r="D64">
-        <v>23.01257286488728</v>
+        <v>22.8220904307817</v>
       </c>
       <c r="E64">
-        <v>19.3656</v>
+        <v>19.7244</v>
       </c>
       <c r="F64">
-        <v>22.2456</v>
+        <v>22.6044</v>
       </c>
       <c r="G64">
         <v>3.69</v>
@@ -7270,37 +7270,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M64">
-        <v>3.265654080000001</v>
+        <v>3.31832592</v>
       </c>
       <c r="N64">
-        <v>-0.3371846922448989</v>
+        <v>-0.3898565322448984</v>
       </c>
       <c r="O64">
-        <v>-0.08935394344489821</v>
+        <v>-0.1033119810448981</v>
       </c>
       <c r="P64">
-        <v>-0.2478307488000007</v>
+        <v>-0.2865445512000003</v>
       </c>
       <c r="Q64">
-        <v>0.4971692511999993</v>
+        <v>0.4584554487999997</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1686970303316865</v>
+        <v>0.1720185716920023</v>
       </c>
       <c r="T64">
-        <v>2.838268598884214</v>
+        <v>2.91497856101622</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2376382705406146</v>
+        <v>0.2338662345002874</v>
       </c>
       <c r="W64">
-        <v>0.1119147018846378</v>
+        <v>0.1124684367753578</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8967481907193003</v>
+        <v>0.8825140924539148</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -7316,22 +7316,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1345019866945163</v>
+        <v>0.1355119866945163</v>
       </c>
       <c r="C65">
-        <v>3.907690430781702</v>
+        <v>3.361535477711296</v>
       </c>
       <c r="D65">
-        <v>22.8220904307817</v>
+        <v>22.6347354777113</v>
       </c>
       <c r="E65">
-        <v>19.7244</v>
+        <v>20.0832</v>
       </c>
       <c r="F65">
-        <v>22.6044</v>
+        <v>22.9632</v>
       </c>
       <c r="G65">
         <v>3.69</v>
@@ -7352,37 +7352,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M65">
-        <v>3.31832592</v>
+        <v>3.37099776</v>
       </c>
       <c r="N65">
-        <v>-0.3898565322448984</v>
+        <v>-0.4425283722448983</v>
       </c>
       <c r="O65">
-        <v>-0.1033119810448981</v>
+        <v>-0.117270018644898</v>
       </c>
       <c r="P65">
-        <v>-0.2865445512000003</v>
+        <v>-0.3252583536000002</v>
       </c>
       <c r="Q65">
-        <v>0.4584554487999997</v>
+        <v>0.4197416463999998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1720185716920023</v>
+        <v>0.1755246431278913</v>
       </c>
       <c r="T65">
-        <v>2.91497856101622</v>
+        <v>2.995950187711116</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2338662345002874</v>
+        <v>0.2302120745862204</v>
       </c>
       <c r="W65">
-        <v>0.1124684367753578</v>
+        <v>0.1130048674507429</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8825140924539148</v>
+        <v>0.8687248097593223</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7398,22 +7398,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1355119866945163</v>
+        <v>0.1365219866945163</v>
       </c>
       <c r="C66">
-        <v>3.361535477711296</v>
+        <v>2.818431608911233</v>
       </c>
       <c r="D66">
-        <v>22.6347354777113</v>
+        <v>22.45043160891123</v>
       </c>
       <c r="E66">
-        <v>20.0832</v>
+        <v>20.442</v>
       </c>
       <c r="F66">
-        <v>22.9632</v>
+        <v>23.322</v>
       </c>
       <c r="G66">
         <v>3.69</v>
@@ -7434,37 +7434,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M66">
-        <v>3.37099776</v>
+        <v>3.423669600000001</v>
       </c>
       <c r="N66">
-        <v>-0.4425283722448983</v>
+        <v>-0.4952002122448986</v>
       </c>
       <c r="O66">
-        <v>-0.117270018644898</v>
+        <v>-0.1312280562448981</v>
       </c>
       <c r="P66">
-        <v>-0.3252583536000002</v>
+        <v>-0.3639721560000005</v>
       </c>
       <c r="Q66">
-        <v>0.4197416463999998</v>
+        <v>0.3810278439999995</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1755246431278913</v>
+        <v>0.1792310615029739</v>
       </c>
       <c r="T66">
-        <v>2.995950187711116</v>
+        <v>3.081548764502862</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2302120745862204</v>
+        <v>0.226670350361817</v>
       </c>
       <c r="W66">
-        <v>0.1130048674507429</v>
+        <v>0.1135247925668853</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8687248097593223</v>
+        <v>0.855359812686102</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7480,22 +7480,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1365219866945163</v>
+        <v>0.1375319866945163</v>
       </c>
       <c r="C67">
-        <v>2.818431608911233</v>
+        <v>2.278304895769566</v>
       </c>
       <c r="D67">
-        <v>22.45043160891123</v>
+        <v>22.26910489576957</v>
       </c>
       <c r="E67">
-        <v>20.442</v>
+        <v>20.8008</v>
       </c>
       <c r="F67">
-        <v>23.322</v>
+        <v>23.6808</v>
       </c>
       <c r="G67">
         <v>3.69</v>
@@ -7516,37 +7516,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M67">
-        <v>3.423669600000001</v>
+        <v>3.476341440000001</v>
       </c>
       <c r="N67">
-        <v>-0.4952002122448986</v>
+        <v>-0.5478720522448985</v>
       </c>
       <c r="O67">
-        <v>-0.1312280562448981</v>
+        <v>-0.1451860938448981</v>
       </c>
       <c r="P67">
-        <v>-0.3639721560000005</v>
+        <v>-0.4026859584000004</v>
       </c>
       <c r="Q67">
-        <v>0.3810278439999995</v>
+        <v>0.3423140415999996</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1792310615029739</v>
+        <v>0.1831555044883555</v>
       </c>
       <c r="T67">
-        <v>3.081548764502862</v>
+        <v>3.172182551694122</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.226670350361817</v>
+        <v>0.2232359511139107</v>
       </c>
       <c r="W67">
-        <v>0.1135247925668853</v>
+        <v>0.1140289623764779</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.855359812686102</v>
+        <v>0.8423998155241913</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7562,22 +7562,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1375319866945163</v>
+        <v>0.1385419866945163</v>
       </c>
       <c r="C68">
-        <v>2.278304895769566</v>
+        <v>1.741083778952383</v>
       </c>
       <c r="D68">
-        <v>22.26910489576957</v>
+        <v>22.09068377895239</v>
       </c>
       <c r="E68">
-        <v>20.8008</v>
+        <v>21.1596</v>
       </c>
       <c r="F68">
-        <v>23.6808</v>
+        <v>24.0396</v>
       </c>
       <c r="G68">
         <v>3.69</v>
@@ -7598,37 +7598,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M68">
-        <v>3.476341440000001</v>
+        <v>3.529013280000001</v>
       </c>
       <c r="N68">
-        <v>-0.5478720522448985</v>
+        <v>-0.6005438922448989</v>
       </c>
       <c r="O68">
-        <v>-0.1451860938448981</v>
+        <v>-0.1591441314448982</v>
       </c>
       <c r="P68">
-        <v>-0.4026859584000004</v>
+        <v>-0.4413997608000007</v>
       </c>
       <c r="Q68">
-        <v>0.3423140415999996</v>
+        <v>0.3036002391999993</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1831555044883555</v>
+        <v>0.1873177925031541</v>
       </c>
       <c r="T68">
-        <v>3.172182551694122</v>
+        <v>3.268309295684853</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2232359511139107</v>
+        <v>0.2199040712465389</v>
       </c>
       <c r="W68">
-        <v>0.1140289623764779</v>
+        <v>0.1145180823410081</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8423998155241913</v>
+        <v>0.8298266839492032</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7644,22 +7644,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1385419866945163</v>
+        <v>0.1395519866945163</v>
       </c>
       <c r="C69">
-        <v>1.741083778952383</v>
+        <v>1.206698974244475</v>
       </c>
       <c r="D69">
-        <v>22.09068377895239</v>
+        <v>21.91509897424448</v>
       </c>
       <c r="E69">
-        <v>21.1596</v>
+        <v>21.5184</v>
       </c>
       <c r="F69">
-        <v>24.0396</v>
+        <v>24.3984</v>
       </c>
       <c r="G69">
         <v>3.69</v>
@@ -7680,37 +7680,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M69">
-        <v>3.529013280000001</v>
+        <v>3.581685120000001</v>
       </c>
       <c r="N69">
-        <v>-0.6005438922448989</v>
+        <v>-0.6532157322448988</v>
       </c>
       <c r="O69">
-        <v>-0.1591441314448982</v>
+        <v>-0.1731021690448982</v>
       </c>
       <c r="P69">
-        <v>-0.4413997608000007</v>
+        <v>-0.4801135632000006</v>
       </c>
       <c r="Q69">
-        <v>0.3036002391999993</v>
+        <v>0.2648864367999993</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1873177925031541</v>
+        <v>0.1917402235188777</v>
       </c>
       <c r="T69">
-        <v>3.268309295684853</v>
+        <v>3.370443961175005</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2199040712465389</v>
+        <v>0.2166701878458545</v>
       </c>
       <c r="W69">
-        <v>0.1145180823410081</v>
+        <v>0.1149928164242286</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8298266839492032</v>
+        <v>0.817623350361715</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7726,22 +7726,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1395519866945163</v>
+        <v>0.1405619866945163</v>
       </c>
       <c r="C70">
-        <v>1.206698974244475</v>
+        <v>0.6750833828448854</v>
       </c>
       <c r="D70">
-        <v>21.91509897424448</v>
+        <v>21.74228338284489</v>
       </c>
       <c r="E70">
-        <v>21.5184</v>
+        <v>21.87720000000001</v>
       </c>
       <c r="F70">
-        <v>24.3984</v>
+        <v>24.7572</v>
       </c>
       <c r="G70">
         <v>3.69</v>
@@ -7762,37 +7762,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M70">
-        <v>3.581685120000001</v>
+        <v>3.634356960000001</v>
       </c>
       <c r="N70">
-        <v>-0.6532157322448988</v>
+        <v>-0.7058875722448992</v>
       </c>
       <c r="O70">
-        <v>-0.1731021690448982</v>
+        <v>-0.1870602066448983</v>
       </c>
       <c r="P70">
-        <v>-0.4801135632000006</v>
+        <v>-0.5188273656000009</v>
       </c>
       <c r="Q70">
-        <v>0.2648864367999993</v>
+        <v>0.2261726343999991</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1917402235188777</v>
+        <v>0.196447972664648</v>
       </c>
       <c r="T70">
-        <v>3.370443961175005</v>
+        <v>3.479167959922586</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2166701878458545</v>
+        <v>0.2135300401959145</v>
       </c>
       <c r="W70">
-        <v>0.1149928164242286</v>
+        <v>0.1154537900992397</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.817623350361715</v>
+        <v>0.8057737365883568</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7808,22 +7808,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1405619866945163</v>
+        <v>0.181542113160297</v>
       </c>
       <c r="C71">
-        <v>0.6750833828448854</v>
+        <v>-4.95403467718074</v>
       </c>
       <c r="D71">
-        <v>21.74228338284489</v>
+        <v>16.47196532281926</v>
       </c>
       <c r="E71">
-        <v>21.87720000000001</v>
+        <v>22.236</v>
       </c>
       <c r="F71">
-        <v>24.7572</v>
+        <v>25.116</v>
       </c>
       <c r="G71">
         <v>3.69</v>
@@ -7844,45 +7844,45 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M71">
-        <v>3.634356960000001</v>
+        <v>5.043292800000001</v>
       </c>
       <c r="N71">
-        <v>-0.7058875722448992</v>
+        <v>-2.114823412244899</v>
       </c>
       <c r="O71">
-        <v>-0.1870602066448983</v>
+        <v>-0.5604282042448981</v>
       </c>
       <c r="P71">
-        <v>-0.5188273656000009</v>
+        <v>-1.554395208</v>
       </c>
       <c r="Q71">
-        <v>0.2261726343999991</v>
+        <v>-0.8093952080000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.196447972664648</v>
+        <v>0.2087033266394054</v>
       </c>
       <c r="T71">
-        <v>3.479167959922586</v>
+        <v>3.762201539016291</v>
       </c>
       <c r="U71">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.2135300401959145</v>
+        <v>0.1538765283973007</v>
       </c>
       <c r="W71">
-        <v>0.1154537900992397</v>
+        <v>0.169901593097822</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.8057737365883568</v>
+        <v>0.5806661448954742</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7890,22 +7890,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.181542113160297</v>
+        <v>0.1830921131602971</v>
       </c>
       <c r="C72">
-        <v>-4.95403467718074</v>
+        <v>-5.462483010792322</v>
       </c>
       <c r="D72">
-        <v>16.47196532281926</v>
+        <v>16.32231698920768</v>
       </c>
       <c r="E72">
-        <v>22.236</v>
+        <v>22.59480000000001</v>
       </c>
       <c r="F72">
-        <v>25.116</v>
+        <v>25.47480000000001</v>
       </c>
       <c r="G72">
         <v>3.69</v>
@@ -7926,37 +7926,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M72">
-        <v>5.043292800000001</v>
+        <v>5.115339840000002</v>
       </c>
       <c r="N72">
-        <v>-2.114823412244899</v>
+        <v>-2.1868704522449</v>
       </c>
       <c r="O72">
-        <v>-0.5604282042448981</v>
+        <v>-0.5795206698448985</v>
       </c>
       <c r="P72">
-        <v>-1.554395208</v>
+        <v>-1.607349782400001</v>
       </c>
       <c r="Q72">
-        <v>-0.8093952080000003</v>
+        <v>-0.8623497824000012</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2087033266394054</v>
+        <v>0.2143206827304194</v>
       </c>
       <c r="T72">
-        <v>3.762201539016291</v>
+        <v>3.891932626568578</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1538765283973007</v>
+        <v>0.1517092533494513</v>
       </c>
       <c r="W72">
-        <v>0.169901593097822</v>
+        <v>0.1703367819274302</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5806661448954742</v>
+        <v>0.5724877484884956</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7972,22 +7972,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.183092113160297</v>
+        <v>0.184642113160297</v>
       </c>
       <c r="C73">
-        <v>-5.462483010792315</v>
+        <v>-5.968236705457805</v>
       </c>
       <c r="D73">
-        <v>16.32231698920769</v>
+        <v>16.17536329454219</v>
       </c>
       <c r="E73">
-        <v>22.5948</v>
+        <v>22.9536</v>
       </c>
       <c r="F73">
-        <v>25.4748</v>
+        <v>25.8336</v>
       </c>
       <c r="G73">
         <v>3.69</v>
@@ -8008,37 +8008,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M73">
-        <v>5.115339840000001</v>
+        <v>5.18738688</v>
       </c>
       <c r="N73">
-        <v>-2.186870452244899</v>
+        <v>-2.258917492244898</v>
       </c>
       <c r="O73">
-        <v>-0.5795206698448981</v>
+        <v>-0.598613135444898</v>
       </c>
       <c r="P73">
-        <v>-1.6073497824</v>
+        <v>-1.6603043568</v>
       </c>
       <c r="Q73">
-        <v>-0.8623497824000005</v>
+        <v>-0.9153043568</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2143206827304193</v>
+        <v>0.22033927854222</v>
       </c>
       <c r="T73">
-        <v>3.891932626568576</v>
+        <v>4.030930220374596</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1517092533494514</v>
+        <v>0.1496021803862645</v>
       </c>
       <c r="W73">
-        <v>0.1703367819274302</v>
+        <v>0.1707598821784381</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5724877484884956</v>
+        <v>0.5645365297594889</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -8054,22 +8054,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.184642113160297</v>
+        <v>0.186192113160297</v>
       </c>
       <c r="C74">
-        <v>-5.968236705457805</v>
+        <v>-6.471367893178041</v>
       </c>
       <c r="D74">
-        <v>16.17536329454219</v>
+        <v>16.03103210682196</v>
       </c>
       <c r="E74">
-        <v>22.9536</v>
+        <v>23.3124</v>
       </c>
       <c r="F74">
-        <v>25.8336</v>
+        <v>26.1924</v>
       </c>
       <c r="G74">
         <v>3.69</v>
@@ -8090,37 +8090,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M74">
-        <v>5.18738688</v>
+        <v>5.259433920000001</v>
       </c>
       <c r="N74">
-        <v>-2.258917492244898</v>
+        <v>-2.330964532244899</v>
       </c>
       <c r="O74">
-        <v>-0.598613135444898</v>
+        <v>-0.6177056010448982</v>
       </c>
       <c r="P74">
-        <v>-1.6603043568</v>
+        <v>-1.713258931200001</v>
       </c>
       <c r="Q74">
-        <v>-0.9153043568</v>
+        <v>-0.9682589312000008</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.22033927854222</v>
+        <v>0.2268036962660059</v>
       </c>
       <c r="T74">
-        <v>4.030930220374596</v>
+        <v>4.180223932240322</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1496021803862645</v>
+        <v>0.1475528354494664</v>
       </c>
       <c r="W74">
-        <v>0.1707598821784381</v>
+        <v>0.1711713906417472</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5645365297594889</v>
+        <v>0.5568031526394958</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -8136,22 +8136,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.186192113160297</v>
+        <v>0.187742113160297</v>
       </c>
       <c r="C75">
-        <v>-6.471367893178041</v>
+        <v>-6.971946154215569</v>
       </c>
       <c r="D75">
-        <v>16.03103210682196</v>
+        <v>15.88925384578443</v>
       </c>
       <c r="E75">
-        <v>23.3124</v>
+        <v>23.6712</v>
       </c>
       <c r="F75">
-        <v>26.1924</v>
+        <v>26.5512</v>
       </c>
       <c r="G75">
         <v>3.69</v>
@@ -8172,37 +8172,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M75">
-        <v>5.259433920000001</v>
+        <v>5.33148096</v>
       </c>
       <c r="N75">
-        <v>-2.330964532244899</v>
+        <v>-2.403011572244898</v>
       </c>
       <c r="O75">
-        <v>-0.6177056010448982</v>
+        <v>-0.6367980666448981</v>
       </c>
       <c r="P75">
-        <v>-1.713258931200001</v>
+        <v>-1.7662135056</v>
       </c>
       <c r="Q75">
-        <v>-0.9682589312000008</v>
+        <v>-1.0212135056</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2268036962660059</v>
+        <v>0.2337653768916216</v>
       </c>
       <c r="T75">
-        <v>4.180223932240322</v>
+        <v>4.341001775788027</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1475528354494664</v>
+        <v>0.1455588782136628</v>
       </c>
       <c r="W75">
-        <v>0.1711713906417472</v>
+        <v>0.1715717772546965</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5568031526394958</v>
+        <v>0.549278785711935</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -8218,22 +8218,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.187742113160297</v>
+        <v>0.189292113160297</v>
       </c>
       <c r="C76">
-        <v>-6.971946154215569</v>
+        <v>-7.470038628943158</v>
       </c>
       <c r="D76">
-        <v>15.88925384578443</v>
+        <v>15.74996137105684</v>
       </c>
       <c r="E76">
-        <v>23.6712</v>
+        <v>24.03</v>
       </c>
       <c r="F76">
-        <v>26.5512</v>
+        <v>26.91</v>
       </c>
       <c r="G76">
         <v>3.69</v>
@@ -8254,37 +8254,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M76">
-        <v>5.33148096</v>
+        <v>5.403528000000001</v>
       </c>
       <c r="N76">
-        <v>-2.403011572244898</v>
+        <v>-2.475058612244899</v>
       </c>
       <c r="O76">
-        <v>-0.6367980666448981</v>
+        <v>-0.6558905322448981</v>
       </c>
       <c r="P76">
-        <v>-1.7662135056</v>
+        <v>-1.81916808</v>
       </c>
       <c r="Q76">
-        <v>-1.0212135056</v>
+        <v>-1.07416808</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2337653768916216</v>
+        <v>0.2412839919672865</v>
       </c>
       <c r="T76">
-        <v>4.341001775788027</v>
+        <v>4.514641846819549</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1455588782136628</v>
+        <v>0.1436180931708139</v>
       </c>
       <c r="W76">
-        <v>0.1715717772546965</v>
+        <v>0.1719614868913006</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.549278785711935</v>
+        <v>0.5419550685691092</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -8300,22 +8300,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.189292113160297</v>
+        <v>0.1908421131602971</v>
       </c>
       <c r="C77">
-        <v>-7.470038628943158</v>
+        <v>-7.965710123860379</v>
       </c>
       <c r="D77">
-        <v>15.74996137105684</v>
+        <v>15.61308987613962</v>
       </c>
       <c r="E77">
-        <v>24.03</v>
+        <v>24.3888</v>
       </c>
       <c r="F77">
-        <v>26.91</v>
+        <v>27.2688</v>
       </c>
       <c r="G77">
         <v>3.69</v>
@@ -8336,37 +8336,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M77">
-        <v>5.403528000000001</v>
+        <v>5.475575040000001</v>
       </c>
       <c r="N77">
-        <v>-2.475058612244899</v>
+        <v>-2.547105652244899</v>
       </c>
       <c r="O77">
-        <v>-0.6558905322448981</v>
+        <v>-0.6749829978448982</v>
       </c>
       <c r="P77">
-        <v>-1.81916808</v>
+        <v>-1.8721226544</v>
       </c>
       <c r="Q77">
-        <v>-1.07416808</v>
+        <v>-1.1271226544</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2412839919672865</v>
+        <v>0.2494291582992567</v>
       </c>
       <c r="T77">
-        <v>4.514641846819549</v>
+        <v>4.702751923770363</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1436180931708139</v>
+        <v>0.1417283814185664</v>
       </c>
       <c r="W77">
-        <v>0.1719614868913006</v>
+        <v>0.1723409410111519</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5419550685691092</v>
+        <v>0.5348240808247788</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8382,22 +8382,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1908421131602971</v>
+        <v>0.1923921131602971</v>
       </c>
       <c r="C78">
-        <v>-7.965710123860379</v>
+        <v>-8.459023212129914</v>
       </c>
       <c r="D78">
-        <v>15.61308987613962</v>
+        <v>15.47857678787009</v>
       </c>
       <c r="E78">
-        <v>24.3888</v>
+        <v>24.7476</v>
       </c>
       <c r="F78">
-        <v>27.2688</v>
+        <v>27.6276</v>
       </c>
       <c r="G78">
         <v>3.69</v>
@@ -8418,37 +8418,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M78">
-        <v>5.475575040000001</v>
+        <v>5.54762208</v>
       </c>
       <c r="N78">
-        <v>-2.547105652244899</v>
+        <v>-2.619152692244898</v>
       </c>
       <c r="O78">
-        <v>-0.6749829978448982</v>
+        <v>-0.694075463444898</v>
       </c>
       <c r="P78">
-        <v>-1.8721226544</v>
+        <v>-1.9250772288</v>
       </c>
       <c r="Q78">
-        <v>-1.1271226544</v>
+        <v>-1.1800772288</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2494291582992567</v>
+        <v>0.2582825999644418</v>
       </c>
       <c r="T78">
-        <v>4.702751923770363</v>
+        <v>4.907219398716901</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1417283814185664</v>
+        <v>0.1398877530884552</v>
       </c>
       <c r="W78">
-        <v>0.1723409410111519</v>
+        <v>0.1727105391798382</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5348240808247788</v>
+        <v>0.5278783135413403</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8464,22 +8464,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1923921131602971</v>
+        <v>0.193942113160297</v>
       </c>
       <c r="C79">
-        <v>-8.459023212129914</v>
+        <v>-8.950038328961298</v>
       </c>
       <c r="D79">
-        <v>15.47857678787009</v>
+        <v>15.34636167103871</v>
       </c>
       <c r="E79">
-        <v>24.7476</v>
+        <v>25.1064</v>
       </c>
       <c r="F79">
-        <v>27.6276</v>
+        <v>27.9864</v>
       </c>
       <c r="G79">
         <v>3.69</v>
@@ -8500,37 +8500,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M79">
-        <v>5.54762208</v>
+        <v>5.619669120000001</v>
       </c>
       <c r="N79">
-        <v>-2.619152692244898</v>
+        <v>-2.691199732244899</v>
       </c>
       <c r="O79">
-        <v>-0.694075463444898</v>
+        <v>-0.7131679290448983</v>
       </c>
       <c r="P79">
-        <v>-1.9250772288</v>
+        <v>-1.978031803200001</v>
       </c>
       <c r="Q79">
-        <v>-1.1800772288</v>
+        <v>-1.233031803200001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2582825999644418</v>
+        <v>0.2679408999628255</v>
       </c>
       <c r="T79">
-        <v>4.907219398716901</v>
+        <v>5.130274825931305</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1398877530884552</v>
+        <v>0.1380943203565519</v>
       </c>
       <c r="W79">
-        <v>0.1727105391798382</v>
+        <v>0.1730706604724044</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5278783135413403</v>
+        <v>0.5211106428549127</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8546,22 +8546,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.193942113160297</v>
+        <v>0.195492113160297</v>
       </c>
       <c r="C80">
-        <v>-8.950038328961298</v>
+        <v>-9.438813862147541</v>
       </c>
       <c r="D80">
-        <v>15.34636167103871</v>
+        <v>15.21638613785246</v>
       </c>
       <c r="E80">
-        <v>25.1064</v>
+        <v>25.4652</v>
       </c>
       <c r="F80">
-        <v>27.9864</v>
+        <v>28.3452</v>
       </c>
       <c r="G80">
         <v>3.69</v>
@@ -8582,37 +8582,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M80">
-        <v>5.619669120000001</v>
+        <v>5.69171616</v>
       </c>
       <c r="N80">
-        <v>-2.691199732244899</v>
+        <v>-2.763246772244898</v>
       </c>
       <c r="O80">
-        <v>-0.7131679290448983</v>
+        <v>-0.7322603946448981</v>
       </c>
       <c r="P80">
-        <v>-1.978031803200001</v>
+        <v>-2.0309863776</v>
       </c>
       <c r="Q80">
-        <v>-1.233031803200001</v>
+        <v>-1.2859863776</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2679408999628255</v>
+        <v>0.2785190380562934</v>
       </c>
       <c r="T80">
-        <v>5.130274825931305</v>
+        <v>5.37457362716613</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1380943203565519</v>
+        <v>0.1363462909849499</v>
       </c>
       <c r="W80">
-        <v>0.1730706604724044</v>
+        <v>0.1734216647702221</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5211106428549127</v>
+        <v>0.5145143056035848</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8628,22 +8628,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.195492113160297</v>
+        <v>0.197042113160297</v>
       </c>
       <c r="C81">
-        <v>-9.438813862147541</v>
+        <v>-9.925406238039635</v>
       </c>
       <c r="D81">
-        <v>15.21638613785246</v>
+        <v>15.08859376196037</v>
       </c>
       <c r="E81">
-        <v>25.4652</v>
+        <v>25.82400000000001</v>
       </c>
       <c r="F81">
-        <v>28.3452</v>
+        <v>28.704</v>
       </c>
       <c r="G81">
         <v>3.69</v>
@@ -8664,37 +8664,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M81">
-        <v>5.69171616</v>
+        <v>5.763763200000001</v>
       </c>
       <c r="N81">
-        <v>-2.763246772244898</v>
+        <v>-2.835293812244899</v>
       </c>
       <c r="O81">
-        <v>-0.7322603946448981</v>
+        <v>-0.7513528602448983</v>
       </c>
       <c r="P81">
-        <v>-2.0309863776</v>
+        <v>-2.083940952000001</v>
       </c>
       <c r="Q81">
-        <v>-1.2859863776</v>
+        <v>-1.338940952000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2785190380562934</v>
+        <v>0.2901549899591081</v>
       </c>
       <c r="T81">
-        <v>5.37457362716613</v>
+        <v>5.643302308524436</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1363462909849499</v>
+        <v>0.1346419623476381</v>
       </c>
       <c r="W81">
-        <v>0.1734216647702221</v>
+        <v>0.1737638939605943</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5145143056035848</v>
+        <v>0.5080828767835399</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8710,22 +8710,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.197042113160297</v>
+        <v>0.1985921131602971</v>
       </c>
       <c r="C82">
-        <v>-9.925406238039635</v>
+        <v>-10.40987000322487</v>
       </c>
       <c r="D82">
-        <v>15.08859376196037</v>
+        <v>14.96292999677513</v>
       </c>
       <c r="E82">
-        <v>25.82400000000001</v>
+        <v>26.1828</v>
       </c>
       <c r="F82">
-        <v>28.704</v>
+        <v>29.0628</v>
       </c>
       <c r="G82">
         <v>3.69</v>
@@ -8746,37 +8746,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M82">
-        <v>5.763763200000001</v>
+        <v>5.835810240000001</v>
       </c>
       <c r="N82">
-        <v>-2.835293812244899</v>
+        <v>-2.907340852244899</v>
       </c>
       <c r="O82">
-        <v>-0.7513528602448983</v>
+        <v>-0.7704453258448982</v>
       </c>
       <c r="P82">
-        <v>-2.083940952000001</v>
+        <v>-2.1368955264</v>
       </c>
       <c r="Q82">
-        <v>-1.338940952000001</v>
+        <v>-1.3918955264</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2901549899591081</v>
+        <v>0.3030157789043244</v>
       </c>
       <c r="T82">
-        <v>5.643302308524436</v>
+        <v>5.940318219499408</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1346419623476381</v>
+        <v>0.1329797158989018</v>
       </c>
       <c r="W82">
-        <v>0.1737638939605943</v>
+        <v>0.1740976730475005</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5080828767835399</v>
+        <v>0.5018102486751012</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8792,22 +8792,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1985921131602971</v>
+        <v>0.2297177854014604</v>
       </c>
       <c r="C83">
-        <v>-10.40987000322487</v>
+        <v>-12.9125657038275</v>
       </c>
       <c r="D83">
-        <v>14.96292999677513</v>
+        <v>12.81903429617251</v>
       </c>
       <c r="E83">
-        <v>26.1828</v>
+        <v>26.54160000000001</v>
       </c>
       <c r="F83">
-        <v>29.0628</v>
+        <v>29.42160000000001</v>
       </c>
       <c r="G83">
         <v>3.69</v>
@@ -8828,45 +8828,45 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M83">
-        <v>5.835810240000001</v>
+        <v>6.937613280000002</v>
       </c>
       <c r="N83">
-        <v>-2.907340852244899</v>
+        <v>-4.0091438922449</v>
       </c>
       <c r="O83">
-        <v>-0.7704453258448982</v>
+        <v>-1.062423131444899</v>
       </c>
       <c r="P83">
-        <v>-2.1368955264</v>
+        <v>-2.946720760800002</v>
       </c>
       <c r="Q83">
-        <v>-1.3918955264</v>
+        <v>-2.201720760800002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3030157789043244</v>
+        <v>0.3221703901832499</v>
       </c>
       <c r="T83">
-        <v>5.940318219499408</v>
+        <v>6.382687994994225</v>
       </c>
       <c r="U83">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1329797158989018</v>
+        <v>0.1118604275612062</v>
       </c>
       <c r="W83">
-        <v>0.1740976730475005</v>
+        <v>0.2094233111810676</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.5018102486751012</v>
+        <v>0.4221148209856835</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8874,22 +8874,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2297177854014604</v>
+        <v>0.2316177854014604</v>
       </c>
       <c r="C84">
-        <v>-12.9125657038275</v>
+        <v>-13.38251206441221</v>
       </c>
       <c r="D84">
-        <v>12.81903429617251</v>
+        <v>12.70788793558779</v>
       </c>
       <c r="E84">
-        <v>26.54160000000001</v>
+        <v>26.9004</v>
       </c>
       <c r="F84">
-        <v>29.42160000000001</v>
+        <v>29.7804</v>
       </c>
       <c r="G84">
         <v>3.69</v>
@@ -8910,37 +8910,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M84">
-        <v>6.937613280000002</v>
+        <v>7.022218320000001</v>
       </c>
       <c r="N84">
-        <v>-4.0091438922449</v>
+        <v>-4.0937489322449</v>
       </c>
       <c r="O84">
-        <v>-1.062423131444899</v>
+        <v>-1.084843467044899</v>
       </c>
       <c r="P84">
-        <v>-2.946720760800002</v>
+        <v>-3.008905465200001</v>
       </c>
       <c r="Q84">
-        <v>-2.201720760800002</v>
+        <v>-2.263905465200001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3221703901832499</v>
+        <v>0.3384274719587353</v>
       </c>
       <c r="T84">
-        <v>6.382687994994225</v>
+        <v>6.758140229993887</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1118604275612062</v>
+        <v>0.1105127115664929</v>
       </c>
       <c r="W84">
-        <v>0.2094233111810676</v>
+        <v>0.209741102612621</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4221148209856835</v>
+        <v>0.4170291002509163</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8956,22 +8956,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2316177854014604</v>
+        <v>0.2335177854014604</v>
       </c>
       <c r="C85">
-        <v>-13.38251206441221</v>
+        <v>-13.85054762207791</v>
       </c>
       <c r="D85">
-        <v>12.70788793558779</v>
+        <v>12.59865237792209</v>
       </c>
       <c r="E85">
-        <v>26.9004</v>
+        <v>27.25920000000001</v>
       </c>
       <c r="F85">
-        <v>29.7804</v>
+        <v>30.13920000000001</v>
       </c>
       <c r="G85">
         <v>3.69</v>
@@ -8992,37 +8992,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M85">
-        <v>7.022218320000001</v>
+        <v>7.106823360000002</v>
       </c>
       <c r="N85">
-        <v>-4.0937489322449</v>
+        <v>-4.178353972244899</v>
       </c>
       <c r="O85">
-        <v>-1.084843467044899</v>
+        <v>-1.107263802644898</v>
       </c>
       <c r="P85">
-        <v>-3.008905465200001</v>
+        <v>-3.071090169600001</v>
       </c>
       <c r="Q85">
-        <v>-2.263905465200001</v>
+        <v>-2.3260901696</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3384274719587353</v>
+        <v>0.3567166889561563</v>
       </c>
       <c r="T85">
-        <v>6.758140229993887</v>
+        <v>7.180523994368507</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1105127115664929</v>
+        <v>0.1091970840478441</v>
       </c>
       <c r="W85">
-        <v>0.209741102612621</v>
+        <v>0.2100513275815184</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4170291002509163</v>
+        <v>0.4120644681050721</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -9038,22 +9038,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2335177854014604</v>
+        <v>0.2354177854014604</v>
       </c>
       <c r="C86">
-        <v>-13.8505476220779</v>
+        <v>-14.31672123200395</v>
       </c>
       <c r="D86">
-        <v>12.5986523779221</v>
+        <v>12.49127876799605</v>
       </c>
       <c r="E86">
-        <v>27.2592</v>
+        <v>27.618</v>
       </c>
       <c r="F86">
-        <v>30.1392</v>
+        <v>30.498</v>
       </c>
       <c r="G86">
         <v>3.69</v>
@@ -9074,37 +9074,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M86">
-        <v>7.106823360000001</v>
+        <v>7.1914284</v>
       </c>
       <c r="N86">
-        <v>-4.178353972244899</v>
+        <v>-4.262959012244899</v>
       </c>
       <c r="O86">
-        <v>-1.107263802644898</v>
+        <v>-1.129684138244898</v>
       </c>
       <c r="P86">
-        <v>-3.071090169600001</v>
+        <v>-3.133274874</v>
       </c>
       <c r="Q86">
-        <v>-2.3260901696</v>
+        <v>-2.388274874</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3567166889561561</v>
+        <v>0.3774444682198999</v>
       </c>
       <c r="T86">
-        <v>7.180523994368501</v>
+        <v>7.659225593993069</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1091970840478441</v>
+        <v>0.1079124124708107</v>
       </c>
       <c r="W86">
-        <v>0.2100513275815184</v>
+        <v>0.2103542531393829</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4120644681050721</v>
+        <v>0.4072166508332478</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -9120,22 +9120,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2354177854014604</v>
+        <v>0.2373177854014604</v>
       </c>
       <c r="C87">
-        <v>-14.31672123200395</v>
+        <v>-14.78108009794638</v>
       </c>
       <c r="D87">
-        <v>12.49127876799605</v>
+        <v>12.38571990205362</v>
       </c>
       <c r="E87">
-        <v>27.618</v>
+        <v>27.9768</v>
       </c>
       <c r="F87">
-        <v>30.498</v>
+        <v>30.8568</v>
       </c>
       <c r="G87">
         <v>3.69</v>
@@ -9156,37 +9156,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M87">
-        <v>7.1914284</v>
+        <v>7.276033440000001</v>
       </c>
       <c r="N87">
-        <v>-4.262959012244899</v>
+        <v>-4.347564052244898</v>
       </c>
       <c r="O87">
-        <v>-1.129684138244898</v>
+        <v>-1.152104473844898</v>
       </c>
       <c r="P87">
-        <v>-3.133274874</v>
+        <v>-3.1954595784</v>
       </c>
       <c r="Q87">
-        <v>-2.388274874</v>
+        <v>-2.4504595784</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3774444682198999</v>
+        <v>0.4011333588070355</v>
       </c>
       <c r="T87">
-        <v>7.659225593993069</v>
+        <v>8.206313136421144</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1079124124708107</v>
+        <v>0.106657616976964</v>
       </c>
       <c r="W87">
-        <v>0.2103542531393829</v>
+        <v>0.2106501339168319</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4072166508332478</v>
+        <v>0.4024815734979775</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -9202,22 +9202,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2373177854014604</v>
+        <v>0.2392177854014604</v>
       </c>
       <c r="C88">
-        <v>-14.78108009794638</v>
+        <v>-15.2436698414308</v>
       </c>
       <c r="D88">
-        <v>12.38571990205362</v>
+        <v>12.2819301585692</v>
       </c>
       <c r="E88">
-        <v>27.9768</v>
+        <v>28.3356</v>
       </c>
       <c r="F88">
-        <v>30.8568</v>
+        <v>31.2156</v>
       </c>
       <c r="G88">
         <v>3.69</v>
@@ -9238,37 +9238,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M88">
-        <v>7.276033440000001</v>
+        <v>7.36063848</v>
       </c>
       <c r="N88">
-        <v>-4.347564052244898</v>
+        <v>-4.432169092244898</v>
       </c>
       <c r="O88">
-        <v>-1.152104473844898</v>
+        <v>-1.174524809444898</v>
       </c>
       <c r="P88">
-        <v>-3.1954595784</v>
+        <v>-3.2576442828</v>
       </c>
       <c r="Q88">
-        <v>-2.4504595784</v>
+        <v>-2.5126442828</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4011333588070355</v>
+        <v>0.4284666940998844</v>
       </c>
       <c r="T88">
-        <v>8.206313136421144</v>
+        <v>8.837567993068925</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.106657616976964</v>
+        <v>0.1054316673565392</v>
       </c>
       <c r="W88">
-        <v>0.2106501339168319</v>
+        <v>0.2109392128373281</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4024815734979775</v>
+        <v>0.3978553485152422</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -9284,22 +9284,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2392177854014604</v>
+        <v>0.2411177854014604</v>
       </c>
       <c r="C89">
-        <v>-15.2436698414308</v>
+        <v>-15.70453456749527</v>
       </c>
       <c r="D89">
-        <v>12.2819301585692</v>
+        <v>12.17986543250473</v>
       </c>
       <c r="E89">
-        <v>28.3356</v>
+        <v>28.6944</v>
       </c>
       <c r="F89">
-        <v>31.2156</v>
+        <v>31.5744</v>
       </c>
       <c r="G89">
         <v>3.69</v>
@@ -9320,37 +9320,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M89">
-        <v>7.36063848</v>
+        <v>7.445243520000001</v>
       </c>
       <c r="N89">
-        <v>-4.432169092244898</v>
+        <v>-4.516774132244899</v>
       </c>
       <c r="O89">
-        <v>-1.174524809444898</v>
+        <v>-1.196945145044898</v>
       </c>
       <c r="P89">
-        <v>-3.2576442828</v>
+        <v>-3.319828987200001</v>
       </c>
       <c r="Q89">
-        <v>-2.5126442828</v>
+        <v>-2.574828987200001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4284666940998844</v>
+        <v>0.4603555852748749</v>
       </c>
       <c r="T89">
-        <v>8.837567993068925</v>
+        <v>9.574031992491337</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1054316673565392</v>
+        <v>0.1042335802274876</v>
       </c>
       <c r="W89">
-        <v>0.2109392128373281</v>
+        <v>0.2112217217823584</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3978553485152422</v>
+        <v>0.393334265009387</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9366,22 +9366,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2411177854014604</v>
+        <v>0.2430177854014604</v>
       </c>
       <c r="C90">
-        <v>-15.70453456749527</v>
+        <v>-16.16371692718224</v>
       </c>
       <c r="D90">
-        <v>12.17986543250473</v>
+        <v>12.07948307281777</v>
       </c>
       <c r="E90">
-        <v>28.6944</v>
+        <v>29.0532</v>
       </c>
       <c r="F90">
-        <v>31.5744</v>
+        <v>31.9332</v>
       </c>
       <c r="G90">
         <v>3.69</v>
@@ -9402,37 +9402,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M90">
-        <v>7.445243520000001</v>
+        <v>7.529848560000001</v>
       </c>
       <c r="N90">
-        <v>-4.516774132244899</v>
+        <v>-4.601379172244899</v>
       </c>
       <c r="O90">
-        <v>-1.196945145044898</v>
+        <v>-1.219365480644898</v>
       </c>
       <c r="P90">
-        <v>-3.319828987200001</v>
+        <v>-3.382013691600001</v>
       </c>
       <c r="Q90">
-        <v>-2.574828987200001</v>
+        <v>-2.6370136916</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4603555852748749</v>
+        <v>0.4980424566634999</v>
       </c>
       <c r="T90">
-        <v>9.574031992491337</v>
+        <v>10.44439853726328</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1042335802274876</v>
+        <v>0.1030624164047068</v>
       </c>
       <c r="W90">
-        <v>0.2112217217823584</v>
+        <v>0.2114978822117702</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.393334265009387</v>
+        <v>0.3889147788856862</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9448,22 +9448,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2430177854014604</v>
+        <v>0.2449177854014604</v>
       </c>
       <c r="C91">
-        <v>-16.16371692718224</v>
+        <v>-16.62125817696541</v>
       </c>
       <c r="D91">
-        <v>12.07948307281777</v>
+        <v>11.98074182303459</v>
       </c>
       <c r="E91">
-        <v>29.0532</v>
+        <v>29.412</v>
       </c>
       <c r="F91">
-        <v>31.9332</v>
+        <v>32.292</v>
       </c>
       <c r="G91">
         <v>3.69</v>
@@ -9484,37 +9484,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M91">
-        <v>7.529848560000001</v>
+        <v>7.614453600000001</v>
       </c>
       <c r="N91">
-        <v>-4.601379172244899</v>
+        <v>-4.685984212244898</v>
       </c>
       <c r="O91">
-        <v>-1.219365480644898</v>
+        <v>-1.241785816244898</v>
       </c>
       <c r="P91">
-        <v>-3.382013691600001</v>
+        <v>-3.444198396</v>
       </c>
       <c r="Q91">
-        <v>-2.6370136916</v>
+        <v>-2.699198396</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4980424566634999</v>
+        <v>0.5432667023298499</v>
       </c>
       <c r="T91">
-        <v>10.44439853726328</v>
+        <v>11.48883839098961</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1030624164047068</v>
+        <v>0.1019172784446545</v>
       </c>
       <c r="W91">
-        <v>0.2114978822117702</v>
+        <v>0.2117679057427505</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3889147788856862</v>
+        <v>0.3845935035647341</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9530,22 +9530,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2449177854014604</v>
+        <v>0.2468177854014604</v>
       </c>
       <c r="C92">
-        <v>-16.62125817696541</v>
+        <v>-17.07719823528578</v>
       </c>
       <c r="D92">
-        <v>11.98074182303459</v>
+        <v>11.88360176471422</v>
       </c>
       <c r="E92">
-        <v>29.412</v>
+        <v>29.7708</v>
       </c>
       <c r="F92">
-        <v>32.292</v>
+        <v>32.6508</v>
       </c>
       <c r="G92">
         <v>3.69</v>
@@ -9566,37 +9566,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M92">
-        <v>7.614453600000001</v>
+        <v>7.699058640000001</v>
       </c>
       <c r="N92">
-        <v>-4.685984212244898</v>
+        <v>-4.7705892522449</v>
       </c>
       <c r="O92">
-        <v>-1.241785816244898</v>
+        <v>-1.264206151844899</v>
       </c>
       <c r="P92">
-        <v>-3.444198396</v>
+        <v>-3.506383100400001</v>
       </c>
       <c r="Q92">
-        <v>-2.699198396</v>
+        <v>-2.761383100400001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5432667023298499</v>
+        <v>0.5985407803665</v>
       </c>
       <c r="T92">
-        <v>11.48883839098961</v>
+        <v>12.76537598998845</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1019172784446545</v>
+        <v>0.1007973083518561</v>
       </c>
       <c r="W92">
-        <v>0.2117679057427505</v>
+        <v>0.2120319946906324</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3845935035647341</v>
+        <v>0.3803672013277588</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9612,22 +9612,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2468177854014604</v>
+        <v>0.2487177854014604</v>
       </c>
       <c r="C93">
-        <v>-17.07719823528578</v>
+        <v>-17.53157573635925</v>
       </c>
       <c r="D93">
-        <v>11.88360176471422</v>
+        <v>11.78802426364075</v>
       </c>
       <c r="E93">
-        <v>29.7708</v>
+        <v>30.12960000000001</v>
       </c>
       <c r="F93">
-        <v>32.6508</v>
+        <v>33.00960000000001</v>
       </c>
       <c r="G93">
         <v>3.69</v>
@@ -9648,37 +9648,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M93">
-        <v>7.699058640000001</v>
+        <v>7.783663680000002</v>
       </c>
       <c r="N93">
-        <v>-4.7705892522449</v>
+        <v>-4.855194292244899</v>
       </c>
       <c r="O93">
-        <v>-1.264206151844899</v>
+        <v>-1.286626487444898</v>
       </c>
       <c r="P93">
-        <v>-3.506383100400001</v>
+        <v>-3.568567804800001</v>
       </c>
       <c r="Q93">
-        <v>-2.761383100400001</v>
+        <v>-2.823567804800001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5985407803665</v>
+        <v>0.6676333779123126</v>
       </c>
       <c r="T93">
-        <v>12.76537598998845</v>
+        <v>14.36104798873701</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1007973083518561</v>
+        <v>0.0997016854349881</v>
       </c>
       <c r="W93">
-        <v>0.2120319946906324</v>
+        <v>0.2122903425744298</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3803672013277588</v>
+        <v>0.3762327752263702</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9694,22 +9694,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2487177854014604</v>
+        <v>0.2506177854014605</v>
       </c>
       <c r="C94">
-        <v>-17.53157573635925</v>
+        <v>-17.98442808140846</v>
       </c>
       <c r="D94">
-        <v>11.78802426364075</v>
+        <v>11.69397191859154</v>
       </c>
       <c r="E94">
-        <v>30.12960000000001</v>
+        <v>30.4884</v>
       </c>
       <c r="F94">
-        <v>33.00960000000001</v>
+        <v>33.3684</v>
       </c>
       <c r="G94">
         <v>3.69</v>
@@ -9730,37 +9730,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M94">
-        <v>7.783663680000002</v>
+        <v>7.868268720000001</v>
       </c>
       <c r="N94">
-        <v>-4.855194292244899</v>
+        <v>-4.939799332244899</v>
       </c>
       <c r="O94">
-        <v>-1.286626487444898</v>
+        <v>-1.309046823044898</v>
       </c>
       <c r="P94">
-        <v>-3.568567804800001</v>
+        <v>-3.630752509200001</v>
       </c>
       <c r="Q94">
-        <v>-2.823567804800001</v>
+        <v>-2.8857525092</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6676333779123126</v>
+        <v>0.7564667176140717</v>
       </c>
       <c r="T94">
-        <v>14.36104798873701</v>
+        <v>16.4126262728423</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0997016854349881</v>
+        <v>0.09862962430127857</v>
       </c>
       <c r="W94">
-        <v>0.2122903425744298</v>
+        <v>0.2125431345897585</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3762327752263702</v>
+        <v>0.3721872615142586</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9776,22 +9776,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2506177854014605</v>
+        <v>0.2525177854014604</v>
       </c>
       <c r="C95">
-        <v>-17.98442808140846</v>
+        <v>-18.43579148746147</v>
       </c>
       <c r="D95">
-        <v>11.69397191859154</v>
+        <v>11.60140851253854</v>
       </c>
       <c r="E95">
-        <v>30.4884</v>
+        <v>30.8472</v>
       </c>
       <c r="F95">
-        <v>33.3684</v>
+        <v>33.7272</v>
       </c>
       <c r="G95">
         <v>3.69</v>
@@ -9812,37 +9812,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M95">
-        <v>7.868268720000001</v>
+        <v>7.952873760000001</v>
       </c>
       <c r="N95">
-        <v>-4.939799332244899</v>
+        <v>-5.024404372244899</v>
       </c>
       <c r="O95">
-        <v>-1.309046823044898</v>
+        <v>-1.331467158644898</v>
       </c>
       <c r="P95">
-        <v>-3.630752509200001</v>
+        <v>-3.6929372136</v>
       </c>
       <c r="Q95">
-        <v>-2.8857525092</v>
+        <v>-2.9479372136</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7564667176140717</v>
+        <v>0.8749111705497504</v>
       </c>
       <c r="T95">
-        <v>16.4126262728423</v>
+        <v>19.14806398498269</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09862962430127857</v>
+        <v>0.09758037297892452</v>
       </c>
       <c r="W95">
-        <v>0.2125431345897585</v>
+        <v>0.2127905480515696</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3721872615142586</v>
+        <v>0.3682278225619794</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9858,22 +9858,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2525177854014604</v>
+        <v>0.2544177854014604</v>
       </c>
       <c r="C96">
-        <v>-18.43579148746147</v>
+        <v>-18.88570103385103</v>
       </c>
       <c r="D96">
-        <v>11.60140851253854</v>
+        <v>11.51029896614897</v>
       </c>
       <c r="E96">
-        <v>30.8472</v>
+        <v>31.20600000000001</v>
       </c>
       <c r="F96">
-        <v>33.7272</v>
+        <v>34.08600000000001</v>
       </c>
       <c r="G96">
         <v>3.69</v>
@@ -9894,37 +9894,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M96">
-        <v>7.952873760000001</v>
+        <v>8.037478800000002</v>
       </c>
       <c r="N96">
-        <v>-5.024404372244899</v>
+        <v>-5.1090094122449</v>
       </c>
       <c r="O96">
-        <v>-1.331467158644898</v>
+        <v>-1.353887494244899</v>
       </c>
       <c r="P96">
-        <v>-3.6929372136</v>
+        <v>-3.755121918000001</v>
       </c>
       <c r="Q96">
-        <v>-2.9479372136</v>
+        <v>-3.010121918000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8749111705497504</v>
+        <v>1.040733404659701</v>
       </c>
       <c r="T96">
-        <v>19.14806398498269</v>
+        <v>22.97767678197924</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09758037297892452</v>
+        <v>0.09655321115809373</v>
       </c>
       <c r="W96">
-        <v>0.2127905480515696</v>
+        <v>0.2130327528089215</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3682278225619794</v>
+        <v>0.3643517402192217</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9940,22 +9940,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2544177854014604</v>
+        <v>0.2563177854014604</v>
       </c>
       <c r="C97">
-        <v>-18.88570103385103</v>
+        <v>-19.33419070653992</v>
       </c>
       <c r="D97">
-        <v>11.51029896614897</v>
+        <v>11.42060929346009</v>
       </c>
       <c r="E97">
-        <v>31.20600000000001</v>
+        <v>31.56480000000001</v>
       </c>
       <c r="F97">
-        <v>34.08600000000001</v>
+        <v>34.44480000000001</v>
       </c>
       <c r="G97">
         <v>3.69</v>
@@ -9976,37 +9976,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M97">
-        <v>8.037478800000002</v>
+        <v>8.122083840000002</v>
       </c>
       <c r="N97">
-        <v>-5.1090094122449</v>
+        <v>-5.193614452244899</v>
       </c>
       <c r="O97">
-        <v>-1.353887494244899</v>
+        <v>-1.376307829844899</v>
       </c>
       <c r="P97">
-        <v>-3.755121918000001</v>
+        <v>-3.817306622400001</v>
       </c>
       <c r="Q97">
-        <v>-3.010121918000001</v>
+        <v>-3.072306622400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.040733404659701</v>
+        <v>1.289466755824627</v>
       </c>
       <c r="T97">
-        <v>22.97767678197924</v>
+        <v>28.72209597747406</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09655321115809373</v>
+        <v>0.09554744854186359</v>
       </c>
       <c r="W97">
-        <v>0.2130327528089215</v>
+        <v>0.2132699116338286</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3643517402192217</v>
+        <v>0.3605564095919381</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -10022,22 +10022,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2563177854014604</v>
+        <v>0.2582177854014605</v>
       </c>
       <c r="C98">
-        <v>-19.33419070653991</v>
+        <v>-19.78129344038989</v>
       </c>
       <c r="D98">
-        <v>11.42060929346009</v>
+        <v>11.33230655961011</v>
       </c>
       <c r="E98">
-        <v>31.5648</v>
+        <v>31.9236</v>
       </c>
       <c r="F98">
-        <v>34.4448</v>
+        <v>34.8036</v>
       </c>
       <c r="G98">
         <v>3.69</v>
@@ -10058,37 +10058,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M98">
-        <v>8.12208384</v>
+        <v>8.206688880000002</v>
       </c>
       <c r="N98">
-        <v>-5.193614452244898</v>
+        <v>-5.278219492244899</v>
       </c>
       <c r="O98">
-        <v>-1.376307829844898</v>
+        <v>-1.398728165444898</v>
       </c>
       <c r="P98">
-        <v>-3.8173066224</v>
+        <v>-3.879491326800001</v>
       </c>
       <c r="Q98">
-        <v>-3.0723066224</v>
+        <v>-3.134491326800001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.289466755824624</v>
+        <v>1.704022341099498</v>
       </c>
       <c r="T98">
-        <v>28.72209597747399</v>
+        <v>38.29612796996532</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09554744854186363</v>
+        <v>0.09456242329916398</v>
       </c>
       <c r="W98">
-        <v>0.2132699116338286</v>
+        <v>0.2135021805860571</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3605564095919382</v>
+        <v>0.3568393332043924</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -10104,22 +10104,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2582177854014605</v>
+        <v>0.2601177854014604</v>
       </c>
       <c r="C99">
-        <v>-19.78129344038989</v>
+        <v>-20.22704115948489</v>
       </c>
       <c r="D99">
-        <v>11.33230655961011</v>
+        <v>11.24535884051512</v>
       </c>
       <c r="E99">
-        <v>31.9236</v>
+        <v>32.2824</v>
       </c>
       <c r="F99">
-        <v>34.8036</v>
+        <v>35.16240000000001</v>
       </c>
       <c r="G99">
         <v>3.69</v>
@@ -10140,37 +10140,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M99">
-        <v>8.206688880000002</v>
+        <v>8.291293920000001</v>
       </c>
       <c r="N99">
-        <v>-5.278219492244899</v>
+        <v>-5.362824532244899</v>
       </c>
       <c r="O99">
-        <v>-1.398728165444898</v>
+        <v>-1.421148501044898</v>
       </c>
       <c r="P99">
-        <v>-3.879491326800001</v>
+        <v>-3.9416760312</v>
       </c>
       <c r="Q99">
-        <v>-3.134491326800001</v>
+        <v>-3.1966760312</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.704022341099498</v>
+        <v>2.533133511649246</v>
       </c>
       <c r="T99">
-        <v>38.29612796996532</v>
+        <v>57.44419195494796</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09456242329916398</v>
+        <v>0.09359750061243782</v>
       </c>
       <c r="W99">
-        <v>0.2135021805860571</v>
+        <v>0.2137297093555872</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3568393332043924</v>
+        <v>0.3531981155186333</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -10186,22 +10186,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2601177854014604</v>
+        <v>0.2620177854014604</v>
       </c>
       <c r="C100">
-        <v>-20.22704115948489</v>
+        <v>-20.67146481561196</v>
       </c>
       <c r="D100">
-        <v>11.24535884051512</v>
+        <v>11.15973518438804</v>
       </c>
       <c r="E100">
-        <v>32.2824</v>
+        <v>32.6412</v>
       </c>
       <c r="F100">
-        <v>35.16240000000001</v>
+        <v>35.5212</v>
       </c>
       <c r="G100">
         <v>3.69</v>
@@ -10222,37 +10222,37 @@
         <v>2.928469387755102</v>
       </c>
       <c r="M100">
-        <v>8.291293920000001</v>
+        <v>8.375898960000001</v>
       </c>
       <c r="N100">
-        <v>-5.362824532244899</v>
+        <v>-5.447429572244898</v>
       </c>
       <c r="O100">
-        <v>-1.421148501044898</v>
+        <v>-1.443568836644898</v>
       </c>
       <c r="P100">
-        <v>-3.9416760312</v>
+        <v>-4.0038607356</v>
       </c>
       <c r="Q100">
-        <v>-3.1966760312</v>
+        <v>-3.2588607356</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.533133511649246</v>
+        <v>5.020467023298493</v>
       </c>
       <c r="T100">
-        <v>57.44419195494796</v>
+        <v>114.8883839098959</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09359750061243782</v>
+        <v>0.09265207131332229</v>
       </c>
       <c r="W100">
-        <v>0.2137297093555872</v>
+        <v>0.2139526415843186</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -10260,91 +10260,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3531981155186333</v>
+        <v>0.3496304577861219</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2620177854014604</v>
-      </c>
-      <c r="C101">
-        <v>-20.67146481561196</v>
-      </c>
-      <c r="D101">
-        <v>11.15973518438804</v>
-      </c>
-      <c r="E101">
-        <v>32.6412</v>
-      </c>
-      <c r="F101">
-        <v>35.5212</v>
-      </c>
-      <c r="G101">
-        <v>3.69</v>
-      </c>
-      <c r="H101">
-        <v>33</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.673469387755102</v>
-      </c>
-      <c r="K101">
-        <v>0.745</v>
-      </c>
-      <c r="L101">
-        <v>2.928469387755102</v>
-      </c>
-      <c r="M101">
-        <v>8.375898960000001</v>
-      </c>
-      <c r="N101">
-        <v>-5.447429572244898</v>
-      </c>
-      <c r="O101">
-        <v>-1.443568836644898</v>
-      </c>
-      <c r="P101">
-        <v>-4.0038607356</v>
-      </c>
-      <c r="Q101">
-        <v>-3.2588607356</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.020467023298493</v>
-      </c>
-      <c r="T101">
-        <v>114.8883839098959</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09265207131332229</v>
-      </c>
-      <c r="W101">
-        <v>0.2139526415843186</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3496304577861219</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
